--- a/docs/downloads/Red_Deer.xlsx
+++ b/docs/downloads/Red_Deer.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D326"/>
+  <dimension ref="A1:D535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -963,17 +963,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Carter</t>
+          <t>Ira</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bennett</t>
+          <t>Stark</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>carterbennett@rocketmail.com</t>
+          <t>iras_ca@hotmail.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -985,17 +985,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Joel</t>
+          <t>Carter</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Luchsinger</t>
+          <t>Bennett</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>hdhobo+1@gmail.com</t>
+          <t>carterbennett@rocketmail.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pelletier</t>
+          <t>Luchsinger</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>reddeercoaching@pickleplexclub.ca</t>
+          <t>hdhobo+1@gmail.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1029,17 +1029,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Joel</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Andrews</t>
+          <t>Pelletier</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>thscp@telusplanet.net</t>
+          <t>reddeercoaching@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1051,17 +1051,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Annette</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mcmillan</t>
+          <t>Andrews</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2moreau@telus.net</t>
+          <t>thscp@telusplanet.net</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Annette</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lim</t>
+          <t>Mcmillan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>noahalim@icloud.com</t>
+          <t>2moreau@telus.net</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1095,17 +1095,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Megan</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nederlof</t>
+          <t>Lim</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>megannederlof1@gmail.com</t>
+          <t>noahalim@icloud.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1117,17 +1117,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Desna</t>
+          <t>Megan</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Karunnyaka</t>
+          <t>Nederlof</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>kddisna@yahoo.com</t>
+          <t>megannederlof1@gmail.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1139,17 +1139,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lesley</t>
+          <t>Desna</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Marriott</t>
+          <t>Karunnyaka</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>lesley_m13@yahoo.ca</t>
+          <t>kddisna@yahoo.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1161,17 +1161,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Arista</t>
+          <t>Lesley</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bouch</t>
+          <t>Marriott</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>bouchpa@gmail.com</t>
+          <t>lesley_m13@yahoo.ca</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pamela</t>
+          <t>Arista</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>Bouch</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>pamelajmiller138@gmail.com</t>
+          <t>bouchpa@gmail.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1205,17 +1205,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kelsie</t>
+          <t>Pamela</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Blackwell</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>kelsie@pickleplexclub.ca</t>
+          <t>pamelajmiller138@gmail.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1227,17 +1227,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sandra</t>
+          <t>Kelsie</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mackie</t>
+          <t>Blackwell</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>aaaa@gmail.com</t>
+          <t>kelsie@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1249,17 +1249,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Sandra</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wyntjes</t>
+          <t>Mackie</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>dylanwynjes@hotmail.com</t>
+          <t>aaaa@gmail.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1271,17 +1271,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Wyntjes</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>wilsonjp76@gmail.com</t>
+          <t>dylanwynjes@hotmail.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1293,17 +1293,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Townsend</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>julie@townsendelectrical.ca</t>
+          <t>wilsonjp76@gmail.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1315,17 +1315,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Tommy jr 2</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Paquette</t>
+          <t>Townsend</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>anthony.paq269+2@gmail.com</t>
+          <t>julie@townsendelectrical.ca</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1337,17 +1337,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Doug</t>
+          <t>Tommy jr 2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dewitt</t>
+          <t>Paquette</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>doug_dewitt@hotmail.com</t>
+          <t>anthony.paq269+2@gmail.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1359,17 +1359,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Laurie</t>
+          <t>Doug</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Hubley</t>
+          <t>DeWitt</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>hubley+1@awink.com</t>
+          <t>doug_dewitt@hotmail.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1381,17 +1381,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jake</t>
+          <t>Laurie</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Brooks</t>
+          <t>Hubley</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jakenb737@gmail.com</t>
+          <t>hubley+1@awink.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1403,17 +1403,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Dick</t>
+          <t>Jake</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Feser</t>
+          <t>Brooks</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>dickfeser@gmail.com</t>
+          <t>jakenb737@gmail.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1425,17 +1425,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Patricia</t>
+          <t>Dick</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lim</t>
+          <t>Feser</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>patricialim19@gmail.com</t>
+          <t>dickfeser@gmail.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1447,17 +1447,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Patricia</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Blair</t>
+          <t>Lim</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>dmboard@telus.net</t>
+          <t>patricialim19@gmail.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1469,17 +1469,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Malika</t>
+          <t>Alayne</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Yohan</t>
+          <t>Farries</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>yohansilba205@gmail.com</t>
+          <t>amfarries@me.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1491,17 +1491,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pochylko</t>
+          <t>Blair</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>lucas@andystrucksales.com</t>
+          <t>dmboard@telus.net</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1513,17 +1513,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Parry</t>
+          <t>Malika</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dyck</t>
+          <t>Yohan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>donutm@telus.net</t>
+          <t>yohansilba205@gmail.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1535,17 +1535,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lim</t>
+          <t>Pochylko</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>bentholim@gmail.com</t>
+          <t>lucas@andystrucksales.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1557,17 +1557,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Parry</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Townsend</t>
+          <t>Dyck</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>scott@townsendelectrical.ca</t>
+          <t>donutm@telus.net</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1579,17 +1579,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Derrek</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Halberson</t>
+          <t>Lim</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>derrekhalberson@gmail.com</t>
+          <t>bentholim@gmail.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1601,17 +1601,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Nikki</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Lastname</t>
+          <t>Townsend</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>chia-fray-1g@icloud.com</t>
+          <t>scott@townsendelectrical.ca</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1623,17 +1623,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Red deer</t>
+          <t>Derrek</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Halberson</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>reddeeraccounting@pickleplexclub.ca</t>
+          <t>derrekhalberson@gmail.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1645,17 +1645,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Nikki</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Monville</t>
+          <t>Lastname</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>thomas@monvillelandscaping.com</t>
+          <t>chia-fray-1g@icloud.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1667,17 +1667,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Red deer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Swenson</t>
+          <t>Accounting</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>gregswenson04@gmail.com</t>
+          <t>reddeeraccounting@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1689,17 +1689,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Kingsley</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Grice</t>
+          <t>Monville</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>grice_kingsley@hotmail.com</t>
+          <t>thomas@monvillelandscaping.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1711,17 +1711,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Doug</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lemieux</t>
+          <t>Swenson</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>djlemieux11@gmail.com</t>
+          <t>gregswenson04@gmail.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1733,17 +1733,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Shayne</t>
+          <t>Kingsley</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Luchsinger</t>
+          <t>Grice</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>hdhobo@gmail.com</t>
+          <t>grice_kingsley@hotmail.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1755,17 +1755,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Antonthy</t>
+          <t>Doug</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Judd</t>
+          <t>Lemieux</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>anthony.judd@ig.ca</t>
+          <t>djlemieux11@gmail.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1777,17 +1777,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Rick</t>
+          <t>Shayne</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Adie</t>
+          <t>Luchsinger</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>hugo2196@proton.me</t>
+          <t>hdhobo@gmail.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1799,17 +1799,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Kris</t>
+          <t>Antonthy</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Krzysik</t>
+          <t>Judd</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>kriskrzysik@hotmail.com</t>
+          <t>anthony.judd@ig.ca</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1821,17 +1821,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>Rick</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Durette</t>
+          <t>Adie</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ejdurett+1@gmail.com</t>
+          <t>hugo2196@proton.me</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1843,17 +1843,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Kris</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Peden</t>
+          <t>Krzysik</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>julieapeden@gmail.com</t>
+          <t>kriskrzysik@hotmail.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1865,17 +1865,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Elena</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Macpherson</t>
+          <t>Durette</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ethanmac@yahoo.ca</t>
+          <t>ejdurett+1@gmail.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1887,17 +1887,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Steven</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Thomlison</t>
+          <t>Peden</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>schrest+2@telusplanet.net</t>
+          <t>julieapeden@gmail.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1909,17 +1909,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Yannick</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Reid</t>
+          <t>Macpherson</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>reidroamer@gmail.com</t>
+          <t>ethanmac@yahoo.ca</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1931,17 +1931,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ava</t>
+          <t>Steven</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bilo</t>
+          <t>Thomlison</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>avabee314@gmail.com</t>
+          <t>schrest+2@telusplanet.net</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Axton</t>
+          <t>Yannick</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Grutterink</t>
+          <t>Reid</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>hjgrutterink+7@hotmail.com</t>
+          <t>reidroamer@gmail.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1975,17 +1975,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Darcy</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Marquart</t>
+          <t>Bilo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>darcymarquart@gmail.com</t>
+          <t>avabee314@gmail.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1997,17 +1997,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Seth</t>
+          <t>Axton</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Gill</t>
+          <t>Grutterink</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>sethg0202@gmail.com</t>
+          <t>hjgrutterink+7@hotmail.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2019,17 +2019,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Benno</t>
+          <t>Darcy</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fath</t>
+          <t>Marquart</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>butse.ls@gmail.com</t>
+          <t>darcymarquart@gmail.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2041,17 +2041,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Seth</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kean</t>
+          <t>Gill</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>bendover@airenet.com</t>
+          <t>sethg0202@gmail.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2063,17 +2063,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Merrill</t>
+          <t>Benno</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Kean</t>
+          <t>Fath</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>merrill@cherryhillauction.com</t>
+          <t>butse.ls@gmail.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2085,17 +2085,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Chay</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Feuser</t>
+          <t>Kean</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>chay_feuser@hotmail.com</t>
+          <t>bendover@airenet.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2107,17 +2107,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Dwayne</t>
+          <t>Merrill</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mcarthur</t>
+          <t>Kean</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>sands1@telusplanet.net</t>
+          <t>merrill@cherryhillauction.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2129,17 +2129,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Chay</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Genereux</t>
+          <t>Feuser</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>emgrose@telus.net</t>
+          <t>chay_feuser@hotmail.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2151,17 +2151,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Dwayne</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Delaronde</t>
+          <t>Mcarthur</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>melissa_delaronde@hotmail.com</t>
+          <t>sands1@telusplanet.net</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2173,17 +2173,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Annie</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Collins</t>
+          <t>Genereux</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>annie.collins0319@gmail.com</t>
+          <t>emgrose@telus.net</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2195,17 +2195,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Langard</t>
+          <t>Delaronde</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>jordanlangard@gmail.com</t>
+          <t>melissa_delaronde@hotmail.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2217,17 +2217,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Yapa</t>
+          <t>Annie</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Banbara</t>
+          <t>Collins</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>yapa1@mail.com</t>
+          <t>annie.collins0319@gmail.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2239,17 +2239,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Holly</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Mundorf</t>
+          <t>Langard</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>theartturtle@gmail.com</t>
+          <t>jordanlangard@gmail.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2261,17 +2261,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Helen</t>
+          <t>Yapa</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Swanson</t>
+          <t>Banbara</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>watercoursewaystudio@gmail.com</t>
+          <t>yapa1@mail.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2283,17 +2283,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Dom</t>
+          <t>Holly</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Gomes</t>
+          <t>Mundorf</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>domgomesmedia@gmail.com</t>
+          <t>theartturtle@gmail.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2305,17 +2305,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sau mei</t>
+          <t>Helen</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>Swanson</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>lamsaumei510@gmail.com</t>
+          <t>watercoursewaystudio@gmail.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2327,15 +2327,19 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Dom</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Pylypets</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
+          <t>Gomes</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>domgomesmedia@gmail.com</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -2345,17 +2349,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Frank</t>
+          <t>Sau mei</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Gallie</t>
+          <t>Lam</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>frank1gallie1@gmail.com</t>
+          <t>lamsaumei510@gmail.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2367,12 +2371,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Nahum</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Pinette</t>
+          <t>Pylypets</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -2385,15 +2389,19 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Carl Michael</t>
+          <t>Frank</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Meneses</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>Gallie</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>frank1gallie1@gmail.com</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -2403,12 +2411,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Nahum</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Lenton</t>
+          <t>Pinette</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -2421,12 +2429,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Carl Michael</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Armstrong</t>
+          <t>Meneses</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -2439,12 +2447,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sydney</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Pillman</t>
+          <t>Lenton</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -2457,12 +2465,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Watt</t>
+          <t>Armstrong</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -2475,19 +2483,15 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Maddie</t>
+          <t>Sydney</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bladds</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>md.blades17@gmail.com</t>
-        </is>
-      </c>
+          <t>Pillman</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -2497,12 +2501,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Reese</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Meikle</t>
+          <t>Watt</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2515,15 +2519,19 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Maddie</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Labrecque</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
+          <t>Bladds</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>md.blades17@gmail.com</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -2533,19 +2541,15 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>andrew</t>
+          <t>Reese</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>feuser</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>andrew.feuser@gmail.com</t>
-        </is>
-      </c>
+          <t>Meikle</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -2555,12 +2559,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Adriana</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>VanLochem</t>
+          <t>Labrecque</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -2573,15 +2577,19 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>andrew</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Blum</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
+          <t>feuser</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>andrew.feuser@gmail.com</t>
+        </is>
+      </c>
       <c r="D100" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -2591,12 +2599,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Criszel</t>
+          <t>Adriana</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Maraon</t>
+          <t>VanLochem</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -2609,12 +2617,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Hailey</t>
+          <t>Aiden</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>Blum</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -2627,12 +2635,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Brooks</t>
+          <t>Criszel</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Hansen</t>
+          <t>Maraon</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -2645,12 +2653,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Paxton</t>
+          <t>Hailey</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -2663,12 +2671,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Taya</t>
+          <t>Brooks</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ferguson</t>
+          <t>Hansen</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -2681,12 +2689,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Paxton</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Glimsdale</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -2699,12 +2707,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>Taya</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Olson</t>
+          <t>Ferguson</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2717,12 +2725,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Bowen</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Glimsdale</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2735,12 +2743,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AJ</t>
+          <t>Aiden</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Celis</t>
+          <t>Olson</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2753,12 +2761,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Steven</t>
+          <t>Bowen</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ruppert</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2771,12 +2779,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>AJ</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Bousquet</t>
+          <t>Celis</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2789,12 +2797,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Devin</t>
+          <t>Steven</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Holzer</t>
+          <t>Ruppert</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2807,12 +2815,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>Bousquet</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2825,12 +2833,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Holzer</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2843,12 +2851,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>VanLochem</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2861,12 +2869,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Liebig</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2879,12 +2887,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Tessa</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>VanLochem</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2897,12 +2905,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Bakker</t>
+          <t>Liebig</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2915,12 +2923,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Tessa</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2933,12 +2941,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Judd</t>
+          <t>Bakker</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2951,12 +2959,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Bovey</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2969,12 +2977,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Michnik</t>
+          <t>Judd</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2987,12 +2995,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Blum</t>
+          <t>Bovey</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -3005,12 +3013,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Jaykob</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Oickle</t>
+          <t>Michnik</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -3023,12 +3031,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ayuno</t>
+          <t>Blum</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -3041,12 +3049,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Gage</t>
+          <t>Jaykob</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Liebig</t>
+          <t>Oickle</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -3059,12 +3067,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Tenley</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>Ayuno</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -3077,12 +3085,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Karston</t>
+          <t>Gage</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Loehndorf</t>
+          <t>Liebig</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -3095,12 +3103,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Bbbb</t>
+          <t>Tenley</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Dorbyk</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -3113,12 +3121,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Vienne</t>
+          <t>Karston</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Wilkening</t>
+          <t>Loehndorf</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -3131,12 +3139,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Bbbb</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Michnik</t>
+          <t>Dorbyk</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -3149,12 +3157,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Vienne</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>VanLochem</t>
+          <t>Wilkening</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -3167,12 +3175,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Alyvia</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>Michnik</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -3185,12 +3193,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Trevor</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Vickery</t>
+          <t>VanLochem</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -3203,12 +3211,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Katelin</t>
+          <t>Alyvia</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Friesen</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -3221,12 +3229,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>Trevor</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Debogorski</t>
+          <t>Vickery</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -3239,12 +3247,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Kolton</t>
+          <t>Katelin</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Balaneski</t>
+          <t>Friesen</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -3257,12 +3265,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Crystal</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Webber</t>
+          <t>Debogorski</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -3275,12 +3283,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MacKenzie</t>
+          <t>Kolton</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Balaneski</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -3293,12 +3301,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Liliam</t>
+          <t>Crystal</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Marinero</t>
+          <t>Webber</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -3311,12 +3319,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Franko</t>
+          <t>MacKenzie</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -3329,12 +3337,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Richelle</t>
+          <t>Liliam</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Hansen</t>
+          <t>Marinero</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -3347,12 +3355,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Ivy</t>
+          <t>Franko</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Bovey</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -3365,7 +3373,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Coen</t>
+          <t>Richelle</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3383,12 +3391,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Madison</t>
+          <t>Ivy</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Judd</t>
+          <t>Bovey</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -3401,12 +3409,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Seth</t>
+          <t>Coen</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Gill</t>
+          <t>Hansen</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -3419,12 +3427,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Adilynn</t>
+          <t>Madison</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Whiles</t>
+          <t>Judd</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -3437,12 +3445,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Seth</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Gill</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -3455,12 +3463,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Braiden</t>
+          <t>Adilynn</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Michnik</t>
+          <t>Whiles</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -3473,12 +3481,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Burke</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -3491,12 +3499,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Jax</t>
+          <t>Braiden</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>Michnik</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -3509,12 +3517,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Burke</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Dore</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -3527,12 +3535,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Jax</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Vickery</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -3545,12 +3553,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Josiah</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Oickle</t>
+          <t>Dore</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -3563,12 +3571,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Webber</t>
+          <t>Vickery</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -3581,12 +3589,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Dion</t>
+          <t>Josiah</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Krause</t>
+          <t>Oickle</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -3599,12 +3607,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Sophia</t>
+          <t>Connor</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Judd</t>
+          <t>Webber</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -3617,12 +3625,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Kenzy</t>
+          <t>Dion</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Koyina</t>
+          <t>Krause</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -3635,12 +3643,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Jill</t>
+          <t>Sophia</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Hamilton</t>
+          <t>Judd</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -3653,12 +3661,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Stetson</t>
+          <t>Kenzy</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Dyck</t>
+          <t>Koyina</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -3671,7 +3679,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Craig</t>
+          <t>Jill</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3689,7 +3697,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Colton</t>
+          <t>Stetson</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3707,12 +3715,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Madyson</t>
+          <t>Craig</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Koyina</t>
+          <t>Hamilton</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -3725,12 +3733,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Harrison</t>
+          <t>Colton</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Simmons</t>
+          <t>Dyck</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -3743,12 +3751,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Madyson</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Froese</t>
+          <t>Koyina</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -3761,12 +3769,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Corbin</t>
+          <t>Harrison</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Dyck</t>
+          <t>Simmons</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -3779,19 +3787,15 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Gunnar</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Kilian</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>gkilian@me.com</t>
-        </is>
-      </c>
+          <t>Froese</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -3801,12 +3805,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Maiya</t>
+          <t>Corbin</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Koyina</t>
+          <t>Dyck</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -3819,15 +3823,19 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Collin</t>
+          <t>Gunnar</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Watts</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr"/>
+          <t>Kilian</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>gkilian@me.com</t>
+        </is>
+      </c>
       <c r="D169" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -3837,19 +3845,15 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Maiya</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Nicoll</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>masonrnicoll@gmail.com</t>
-        </is>
-      </c>
+          <t>Koyina</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -3859,12 +3863,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Jin Yu</t>
+          <t>Collin</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Liang</t>
+          <t>Watts</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -3877,17 +3881,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Tracy</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>McClelland</t>
+          <t>Nicoll</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>tracym1@telus.net</t>
+          <t>masonrnicoll@gmail.com</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -3899,19 +3903,15 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Dianne</t>
+          <t>Jin Yu</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Gomes</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>dianne.gomes1@gmail.com</t>
-        </is>
-      </c>
+          <t>Liang</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -3921,17 +3921,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Jody</t>
+          <t>Tracy</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Muth</t>
+          <t>McClelland</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>gramadoes@gmail.com</t>
+          <t>tracym1@telus.net</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -3943,17 +3943,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Eoin</t>
+          <t>Dianne</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Wolfe</t>
+          <t>Gomes</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>wolfeeion@gmail.com</t>
+          <t>dianne.gomes1@gmail.com</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -3965,15 +3965,19 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Clõy</t>
+          <t>Jody</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Jones</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr"/>
+          <t>Muth</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>gramadoes@gmail.com</t>
+        </is>
+      </c>
       <c r="D176" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -3983,15 +3987,19 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Brielle</t>
+          <t>Eoin</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Tweten</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr"/>
+          <t>Wolfe</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>wolfeeion@gmail.com</t>
+        </is>
+      </c>
       <c r="D177" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4001,12 +4009,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Bennett</t>
+          <t>Clõy</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -4019,12 +4027,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Teagan</t>
+          <t>Brielle</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Coulter</t>
+          <t>Tweten</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -4037,12 +4045,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Kinley</t>
+          <t>Bennett</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Coulter</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -4055,12 +4063,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>McKinley</t>
+          <t>Teagan</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Coulter</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -4073,12 +4081,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Maris</t>
+          <t>Kinley</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Epp</t>
+          <t>Coulter</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -4091,12 +4099,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>McKinley</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Polachek</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -4109,12 +4117,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Maris</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Tweten</t>
+          <t>Epp</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -4127,19 +4135,15 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Krywik</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>cad.support.contractors@gmail.com</t>
-        </is>
-      </c>
+          <t>Polachek</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4149,12 +4153,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Kayla</t>
+          <t>Hunter</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Tweten</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -4167,15 +4171,19 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Joel</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Peterman</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr"/>
+          <t>Krywik</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>cad.support.contractors@gmail.com</t>
+        </is>
+      </c>
       <c r="D187" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4185,12 +4193,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Chase</t>
+          <t>Kayla</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Girletz</t>
+          <t>Lane</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -4203,12 +4211,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Stratten</t>
+          <t>Joel</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Girletz</t>
+          <t>Peterman</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -4221,12 +4229,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Gavin</t>
+          <t>Chase</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Girletz</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -4239,12 +4247,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Stratten</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Kosola</t>
+          <t>Girletz</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -4257,12 +4265,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Danté</t>
+          <t>Gavin</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -4275,12 +4283,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Brent</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>Kosola</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -4293,12 +4301,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Rowyn</t>
+          <t>Danté</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Girletz</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -4311,12 +4319,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Sheldon</t>
+          <t>Brent</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Young</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -4329,12 +4337,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Mackenzie</t>
+          <t>Rowyn</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Differenz</t>
+          <t>Girletz</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -4347,7 +4355,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Quinn</t>
+          <t>Sheldon</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4365,12 +4373,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Vera</t>
+          <t>Mackenzie</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Kosola</t>
+          <t>Differenz</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -4383,19 +4391,15 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Clint</t>
+          <t>Quinn</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Buswell</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>clintbuswell@gmail.com</t>
-        </is>
-      </c>
+          <t>Lane</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4405,19 +4409,15 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Rebeca</t>
+          <t>Vera</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Buswell</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>rebecabuswell@gmail.com</t>
-        </is>
-      </c>
+          <t>Kosola</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4427,17 +4427,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Clint</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Brownell</t>
+          <t>Buswell</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>emersonbrownell@gmail.com</t>
+          <t>clintbuswell@gmail.com</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -4449,17 +4449,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Carla</t>
+          <t>Rebeca</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Mccrae</t>
+          <t>Buswell</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>carlanmccrae@gmail.com</t>
+          <t>rebecabuswell@gmail.com</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -4471,7 +4471,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>brownel+@telus.net</t>
+          <t>emersonbrownell@gmail.com</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -4493,17 +4493,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Carla</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Treu</t>
+          <t>Mccrae</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>ltreu@telus.net</t>
+          <t>carlanmccrae@gmail.com</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -4515,15 +4515,19 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Kang</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr"/>
+          <t>Brownell</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>brownel+@telus.net</t>
+        </is>
+      </c>
       <c r="D205" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4533,15 +4537,19 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Beau</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Becker</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr"/>
+          <t>Treu</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>ltreu@telus.net</t>
+        </is>
+      </c>
       <c r="D206" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4556,14 +4564,10 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Huang</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>andrehuang74@gmail.com</t>
-        </is>
-      </c>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4573,12 +4577,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Li Juan</t>
+          <t>Beau</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Tong</t>
+          <t>Becker</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -4591,17 +4595,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>artur</t>
+          <t>Kang</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Hayrepetyan</t>
+          <t>Huang</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>hayreptyan1115@gmail.com</t>
+          <t>andrehuang74@gmail.com</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -4613,12 +4617,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Emersyn</t>
+          <t>Li Juan</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Spina</t>
+          <t>Tong</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -4631,15 +4635,19 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Ruth</t>
+          <t>artur</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Howley</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr"/>
+          <t>Hayrepetyan</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>hayreptyan1115@gmail.com</t>
+        </is>
+      </c>
       <c r="D211" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4649,12 +4657,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Camryn</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Spina</t>
+          <t>Sopkow</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -4667,12 +4675,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Piper</t>
+          <t>Emersyn</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Watt</t>
+          <t>Spina</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -4685,12 +4693,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Ruth</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Schurek</t>
+          <t>Howley</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -4703,12 +4711,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Adelyn</t>
+          <t>Camryn</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Visser</t>
+          <t>Spina</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -4721,12 +4729,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Harper</t>
+          <t>Piper</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Harnett</t>
+          <t>Watt</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -4739,12 +4747,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Blake</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Watt</t>
+          <t>Schurek</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -4757,12 +4765,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Renn</t>
+          <t>Adelyn</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Schurek</t>
+          <t>Visser</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -4775,12 +4783,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Lauren</t>
+          <t>Harper</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Sopkow</t>
+          <t>Harnett</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -4793,7 +4801,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Brynn</t>
+          <t>Blake</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -4811,7 +4819,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Jayde</t>
+          <t>Renn</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -4829,7 +4837,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Kate</t>
+          <t>Lauren</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -4847,12 +4855,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Makenna</t>
+          <t>Brynn</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Watt</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -4865,12 +4873,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Lainey</t>
+          <t>Jayde</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Klassen</t>
+          <t>Schurek</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -4883,12 +4891,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Kate</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Klassen</t>
+          <t>Sopkow</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -4901,12 +4909,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Bryn</t>
+          <t>Makenna</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -4919,7 +4927,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Lainey</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -4937,19 +4945,15 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Bailey</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>kirstenwestberg+111@gmail.com</t>
-        </is>
-      </c>
+          <t>Klassen</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4959,12 +4963,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Abbiegale</t>
+          <t>Bryn</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Hunter</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -4977,19 +4981,15 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Sandi</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>O'Brien</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>sandals_84@hotmail.com</t>
-        </is>
-      </c>
+          <t>Klassen</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4999,15 +4999,19 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Bbbb</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Dorbyk</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr"/>
+          <t>Bailey</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>kirstenwestberg+111@gmail.com</t>
+        </is>
+      </c>
       <c r="D231" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -5017,7 +5021,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Paxton</t>
+          <t>Abbiegale</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5035,15 +5039,19 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Madison</t>
+          <t>Sandi</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Judd</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr"/>
+          <t>O'Brien</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>sandals_84@hotmail.com</t>
+        </is>
+      </c>
       <c r="D233" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -5053,12 +5061,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>Bbbb</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Debogorski</t>
+          <t>Dorbyk</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -5071,12 +5079,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Tenley</t>
+          <t>Paxton</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -5089,12 +5097,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>Madison</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Blum</t>
+          <t>Judd</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -5107,12 +5115,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Olson</t>
+          <t>Debogorski</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -5125,12 +5133,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Crystal</t>
+          <t>Tenley</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Webber</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -5143,12 +5151,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Alyvia</t>
+          <t>Aiden</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>Blum</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -5161,12 +5169,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Adriana</t>
+          <t>Aiden</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>VanLochem</t>
+          <t>Olson</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -5179,12 +5187,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Trevor</t>
+          <t>Crystal</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Vickery</t>
+          <t>Webber</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -5197,12 +5205,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Hailey</t>
+          <t>Alyvia</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -5215,12 +5223,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Adriana</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Ayuno</t>
+          <t>VanLochem</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -5233,12 +5241,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Jax</t>
+          <t>Trevor</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>Vickery</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -5251,12 +5259,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Tessa</t>
+          <t>Hailey</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -5269,12 +5277,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Josiah</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Oickle</t>
+          <t>Ayuno</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -5287,12 +5295,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Dion</t>
+          <t>Jax</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Krause</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -5305,12 +5313,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Vienne</t>
+          <t>Tessa</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Wilkening</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -5323,7 +5331,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Jaykob</t>
+          <t>Josiah</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5341,12 +5349,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Dion</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>VanLochem</t>
+          <t>Krause</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -5359,12 +5367,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Vienne</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Blum</t>
+          <t>Wilkening</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -5377,12 +5385,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Gage</t>
+          <t>Jaykob</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Liebig</t>
+          <t>Oickle</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -5395,12 +5403,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>VanLochem</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -5413,12 +5421,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Blum</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -5431,12 +5439,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>AJ</t>
+          <t>Gage</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Celis</t>
+          <t>Liebig</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -5449,12 +5457,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Adilynn</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Whiles</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -5467,12 +5475,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Bovey</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -5485,12 +5493,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Taya</t>
+          <t>AJ</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Ferguson</t>
+          <t>Celis</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -5503,12 +5511,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Adilynn</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Glimsdale</t>
+          <t>Whiles</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -5521,12 +5529,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Braiden</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Michnik</t>
+          <t>Bovey</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -5539,12 +5547,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Taya</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>VanLochem</t>
+          <t>Ferguson</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -5557,12 +5565,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Liliam</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Marinero</t>
+          <t>Glimsdale</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -5575,12 +5583,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Richelle</t>
+          <t>Braiden</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Hansen</t>
+          <t>Michnik</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -5593,12 +5601,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Judd</t>
+          <t>VanLochem</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -5611,12 +5619,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Seth</t>
+          <t>Liliam</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Gill</t>
+          <t>Marinero</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -5629,12 +5637,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Richelle</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Bousquet</t>
+          <t>Hansen</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -5647,12 +5655,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Judd</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -5665,12 +5673,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Seth</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Michnik</t>
+          <t>Gill</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -5683,12 +5691,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Vickery</t>
+          <t>Bousquet</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -5701,12 +5709,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Kolton</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Balaneski</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
@@ -5719,12 +5727,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Sophia</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Judd</t>
+          <t>Michnik</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -5737,12 +5745,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>MacKenzie</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Vickery</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -5755,12 +5763,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Brooks</t>
+          <t>Kolton</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Hansen</t>
+          <t>Balaneski</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -5773,12 +5781,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>Sophia</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Webber</t>
+          <t>Judd</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -5791,12 +5799,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Karston</t>
+          <t>MacKenzie</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Loehndorf</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -5809,12 +5817,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Criszel</t>
+          <t>Brooks</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Maraon</t>
+          <t>Hansen</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -5827,12 +5835,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Franko</t>
+          <t>Connor</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Webber</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
@@ -5845,12 +5853,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Karston</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Michnik</t>
+          <t>Loehndorf</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -5863,12 +5871,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Criszel</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Maraon</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -5881,12 +5889,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Burke</t>
+          <t>Franko</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -5899,12 +5907,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Liebig</t>
+          <t>Michnik</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
@@ -5917,12 +5925,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Ivy</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Bovey</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
@@ -5935,12 +5943,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Burke</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dore</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -5953,12 +5961,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Bowen</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Liebig</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -5971,12 +5979,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Steven</t>
+          <t>Ivy</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Ruppert</t>
+          <t>Bovey</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -5989,12 +5997,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Coen</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Hansen</t>
+          <t>Dore</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -6007,12 +6015,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Bowen</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Bakker</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -6025,12 +6033,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Katelin</t>
+          <t>Steven</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Friesen</t>
+          <t>Ruppert</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -6043,12 +6051,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Devin</t>
+          <t>Coen</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Holzer</t>
+          <t>Hansen</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
@@ -6061,12 +6069,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Dean</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Lunde</t>
+          <t>Bakker</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
@@ -6079,19 +6087,15 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Brenda</t>
+          <t>Katelin</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Wyntjes</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>pipercreekpetresort@outlook.com</t>
-        </is>
-      </c>
+          <t>Friesen</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6101,12 +6105,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Brady</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Maaskant</t>
+          <t>Holzer</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
@@ -6119,12 +6123,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Christ</t>
+          <t>Dean</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Keumoe</t>
+          <t>Lunde</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
@@ -6137,15 +6141,19 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Pedro</t>
+          <t>Brenda</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Bazzan</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr"/>
+          <t>Wyntjes</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>pipercreekpetresort@outlook.com</t>
+        </is>
+      </c>
       <c r="D294" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6155,12 +6163,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Linden</t>
+          <t>Brady</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Skrodolis</t>
+          <t>Maaskant</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
@@ -6173,12 +6181,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Zylah</t>
+          <t>Christ</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Bizimana</t>
+          <t>Keumoe</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
@@ -6191,19 +6199,15 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Danielle</t>
+          <t>Pedro</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Haessel</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>danielleparker482@hotmail.com</t>
-        </is>
-      </c>
+          <t>Bazzan</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6213,7 +6217,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>Linden</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -6231,19 +6235,15 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Craig</t>
+          <t>Zylah</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Gomez</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>craig.shawn.gomez@gmail.com</t>
-        </is>
-      </c>
+          <t>Bizimana</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6253,17 +6253,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Danielle</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Gizikoff</t>
+          <t>Haessel</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>info@lepagephc.ca</t>
+          <t>danielleparker482@hotmail.com</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -6275,12 +6275,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Ellie</t>
+          <t>Connor</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Glover</t>
+          <t>Skrodolis</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
@@ -6293,15 +6293,19 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Wendy</t>
+          <t>Craig</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Glover</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr"/>
+          <t>Gomez</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>craig.shawn.gomez@gmail.com</t>
+        </is>
+      </c>
       <c r="D302" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6311,15 +6315,19 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Glover</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr"/>
+          <t>Gizikoff</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>info@lepagephc.ca</t>
+        </is>
+      </c>
       <c r="D303" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6329,17 +6337,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Shakil</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Papel</t>
+          <t>Yaholkoski</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>sk17papel@gmail.com</t>
+          <t>jason@fitnessinthehome.com</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -6351,12 +6359,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Alyssa</t>
+          <t>Ellie</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Sherwin</t>
+          <t>Glover</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
@@ -6369,12 +6377,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Seth</t>
+          <t>Wendy</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Gill</t>
+          <t>Glover</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
@@ -6387,12 +6395,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Jai-Li</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Harvey</t>
+          <t>Glover</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
@@ -6405,15 +6413,19 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Raine</t>
+          <t>Shakil</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Joson</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr"/>
+          <t>Papel</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>sk17papel@gmail.com</t>
+        </is>
+      </c>
       <c r="D308" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6423,12 +6435,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Isaac</t>
+          <t>Alyssa</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Park</t>
+          <t>Sherwin</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
@@ -6441,12 +6453,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Fisher</t>
+          <t>Seth</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Dunphy</t>
+          <t>Gill</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
@@ -6459,12 +6471,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Ayden</t>
+          <t>Jai-Li</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Quinlan</t>
+          <t>Harvey</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
@@ -6477,12 +6489,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>Raine</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>Joson</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
@@ -6495,12 +6507,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Marah</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Dunphy</t>
+          <t>Park</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
@@ -6513,12 +6525,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Fisher</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Fleck</t>
+          <t>Dunphy</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
@@ -6531,12 +6543,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Ayden</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>McRae</t>
+          <t>Quinlan</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
@@ -6549,19 +6561,15 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Hanna</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Safron</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>hannasafron@icloud.com</t>
-        </is>
-      </c>
+          <t>Kennedy</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6571,12 +6579,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Marah</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Howard</t>
+          <t>Dunphy</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
@@ -6589,19 +6597,15 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Mila</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Haynes</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>cristinabagundol@yahoo.com</t>
-        </is>
-      </c>
+          <t>Fleck</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6611,12 +6615,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Robberstad</t>
+          <t>McRae</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
@@ -6629,15 +6633,19 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Shayne</t>
+          <t>Hanna</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Malsbury</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr"/>
+          <t>Safron</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>hannasafron@icloud.com</t>
+        </is>
+      </c>
       <c r="D320" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6647,12 +6655,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>McClelland</t>
+          <t>Howard</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
@@ -6665,15 +6673,19 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Larry</t>
+          <t>Mila</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Vetter</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr"/>
+          <t>Haynes</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>cristinabagundol@yahoo.com</t>
+        </is>
+      </c>
       <c r="D322" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6683,12 +6695,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Vetter</t>
+          <t>Robberstad</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
@@ -6701,12 +6713,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Shayne</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Fuchs</t>
+          <t>Malsbury</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
@@ -6719,12 +6731,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Meyer</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Fuchs</t>
+          <t>McClelland</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
@@ -6737,20 +6749,4542 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
+          <t>Larry</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Vetter</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr"/>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Vetter</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Fuchs</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Meyer</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Fuchs</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Serenna</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Constable</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>reddeer@bredin.ca</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Carter</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Proft</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>carter.proft@iaprivatewealth.ca</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
           <t>Sakthi</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
+      <c r="B332" t="inlineStr">
         <is>
           <t>Aenugula</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr">
+      <c r="C332" t="inlineStr">
         <is>
           <t>sakthiprasanth.aenugula@novachem.com</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr">
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Nikki</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Januszewski</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Buffy</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Robblee</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Zoey</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Januszewski</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Brooke</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>McPeek</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Ella</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Januszewski</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Barb</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Pfannmueler</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Adyson</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Trepanier</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Eric</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Trepanier</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Trepanier</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Megan &amp; John</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Heinen</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>maheinen84@gmail.com</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Cote</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Jayda</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Differenz</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>julien</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>kellyseamus=+1@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Davison</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>jldav78@gmail.com</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Kaitlin</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Meier</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>kmeier@pivotalcpa.ca</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Tristin</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Brisbois</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>tristin.brisbois@reddeer.ca</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Charlene</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Parcels</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>ashley_parcels21+1@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Luke</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Escobar</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>escobar8765@gmail.com</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Alison</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Kelly</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>areweeoran@gmail.com</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Cinzia</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Gaudelli</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>cinzia.gaudelli@gmial.com</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Amy</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Musuronchan</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>clientcare@trilliantrealty.ca</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Jaclyn</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Parcels</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>beandeane21@gmail.com</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Jeff</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Dell</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>jeffgdell@gmail.com</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Fatima</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Hilario</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>f.hilario1997@gmail.com</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Ashley</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Parcels</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>ashley_parcels21@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Danny</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Benfeito</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>dannybenfeito929@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Lane</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>lanemenard@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Simon</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Escobar</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>sbescobar@outlook.com</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Kiril</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Serbin</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>kirilkse@gmail.com</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Maksym</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Mamonov</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>vkmra@gmail.com</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Barnabe</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>lbarnabe432@gmail.com</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Frankie</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Cummings</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>fbradley@fibreop.ca</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Kade</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Doyle</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>kadepdoyle@gmail.com</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Aleigha</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Seguin</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>aleighaseguin@gmail.com</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>anthony.daniel07@icloud.com</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Abby</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Schetszle</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>aschetza@gmail.com</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Kade</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Garritty</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>kadegarrity16@gmail.com</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Pat</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Garritty</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>pat@tirlliantreality.ca</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Yuen</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>annayuen@nanjing-school.com</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Rian</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Morin</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>rian2003morin@gmail.com</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Gianfranco Miguel</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Quiballo</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>gianquiballo.rpmmc@gmail.com</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Garry</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Lightbrown</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>glightbrown1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Madison</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Caine</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>madisonlcaine@gmail.com</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>leslie</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>wright</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>leslie0985@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Natalya</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Agafomov</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>natase29@msn.com</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>serozho</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>agafonon</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>serozhoagafonon@gmail.com</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>sergeui</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>agafonod</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>matase29+1@msn.com</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Hopp</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>kristen@hopp.ca</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Fraser</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>fraser211@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Teigan</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>McAuley</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>teigs100770@gmail.com</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Dave</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Macdermid</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>dave.macdermid@novachem.com</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Hanz Izaac</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Villanueva</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>hanzvillanueva@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Shane</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Amundson</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>shane97a@icloud.com</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Arturo</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Raynoso</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>arturo.raynoso@gmail.com</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Lorie</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Fritz</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>lorifritz03@gmail.com</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Ejiro</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Oghenovo</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>oghenovosion@gmail.com</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Oosterhoff</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>aoosterhoff1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Jackie</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Hofseth</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>jackie.hofseth@novachem.com</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Gary</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>gary.murray@novachem.com</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>taylor.mitchell.green@gmail.com</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Gerald</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>gerladalexander@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Zengshan</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Gui</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>gui_jason@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Yash</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Kapil</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>yashkapil@novachem.com</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Boyer</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>alex.d.boyer@gmail.com</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Joel</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Varghese</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>joelvarghesecanada@gmail.com</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Sergio</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Mojica</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>sergiomojica@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Jason</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Liptak</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>jason.liptak@novachem.com</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Trent</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>lotgreen@hotmail.ca</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Ramirez</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>juan.ramirez@novachem.com</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Connor</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Einhorn</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>ceinhorn9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Sesak</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>ambersesak06@outlook.com</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Tone</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>angtone@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Visser</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>blackpanther_26@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Einhorn</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>meinhorn@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Frey</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>stvfrey2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Carrie</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Turney</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>carrie.sue15@gmail.com</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Brooklynn</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>brookfritz1993@gmail.com</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Marceno</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Nembhard</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>marceno.nembhard@gmail.com</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Juliet</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Mojica</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>jumojicabarboza@gmail.com</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Vincent</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Soong</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>vincentsoong@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Mojica</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>ammbsx@gmail.com</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Sunni</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Yeow</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>sunni@createmethod.com</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Tutu</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>H.</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>tutuyyc@gmail.com</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Doofus</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Cheng</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>sundayrosenine9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Adlina</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Yeow</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>adlina@createmethod.com</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Fernanda</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Mojica</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>fernandamojicanoriega2007@gmail.com</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Jolly</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Hilay</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>jaih09@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Teryn</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Chan</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>terynchan@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Gordon</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Chan</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>gor.cha@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Spady</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>jacksonkspady@gmail.com</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Merric</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Roe</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>merricroe@icloud.com</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Abe</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Halvorsen</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>faberconstruction.abe@gmail.com</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Kayla</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Hebert</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>kayla.c.harrison@gmail.com</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Ava</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Spady</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>avaspady@gmail.com</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Elizabeth</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Wong</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>wong.liza24@gmail.com</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Lacroix</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>emmalacroix834@gmail.com</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Edgar</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Herman</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>edgarhermanm@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Robert</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Lauze</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>robert.lauze16@gmail.com</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Shelley</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Lauze</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>shelley.lauze1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Hunter</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Frank</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Young</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>borodoc13@gmail.com</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>chris</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>lewis</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>clewis@cjcedm.ca</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>vera</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>allen</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>lallen5+1@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>linda</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>allen</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>lallen5@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Emily</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Uebell</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>etuebell@gmail.com</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Kristin</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Quinn</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>kirstin.quinn23@gmail.com</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Anita</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Lode</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>nitz.lobe@gmail.com</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Sou</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Hassan</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>souad.hassan992@gmail.com</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Kaitlyn</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Blaire</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>kaitlynblaire22@icloud.com</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Alexandra</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Hobbs</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>alekhobbs@gmail.com</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Caroline</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Panteluk</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>panteluk@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Mario</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Gallant</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>mario.gallant@icloud.com</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Juila</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Vrotla</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>julia.vrotla@gmail.com</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Iryna</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Dinou</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>iryna.dinou@gmail.com</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>belich</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>emmabelich94@gmail.com</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Rod</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Dand</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>rcdand@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Will</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Fierro</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>fierro1007@gmail.com</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Chan</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>joechan3@gmail.com</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Joan</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Skiba</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>jskiba1@telus.net</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Emree</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Hart</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>meaghart@gmail.com</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Lundmark</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>liam.lime35@gmail.com</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Edwards</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>rcedwards58@gmail.com</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Archer</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>hotsauceboss97@icloud.com</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Atlas</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Phadilla</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>tweetaaron+1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Garry</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Macintosh</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>macintoshgarry@gmail.com</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Fierro</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>nicegmoreno@gmail.com</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Abby</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Holland</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>abby.holland@gmail.com</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Snider</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>snider.jason@gmail.com</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Fox</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>fox60113@gmail.com</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Clayton</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Watmough</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>claytonw@gibsonsbuilding.com</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Jaycob</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Ocol</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>jaycobalverto2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Helfmann</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>richardhelfmann@gmail.com</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Sai Srivibhav</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Swayampakula</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>chaitusvk@gmail.com</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Seija</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Worth</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Elias</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Worth</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Derrick</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>jderrick921@gmail.com</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Frances</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Rovero</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>francesrovero45@gmail.com</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Rovero</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>jvcrovero01@gmail.com</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>WAYNE</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>PANSEGRAM</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>wayne@topshelfarena.com</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Palalon</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>daryljay1985@gmail.com</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Jason</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Biondo</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>jbiondodc@gmail.com</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Rhenz</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Viterbo</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>rhenzgabriel@gmail.com</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>quinn</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>whitecotton</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>mattwhitecotton+1@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>london</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>adcock</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>mattwhitecotton+4@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>cayson</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>waddell</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>mattwhitecotton+2@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>devyn</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>whitecotton</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>mattwhitecotton+5@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Khryzzia Kaye</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Mendio</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>mendio.kaye@gmail.com</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>McCuaig</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>mccuaigranch@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Ines</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Brennan</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>brennanines@gmail.com</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Brandi</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Middel</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>brandimiddel@gmail.com</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Devan</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Krahn</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>de_vo_brown@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>cainsley</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>coleman</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>mattwhitecotton+3@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Jyzzle</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Rosano</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>jhinengskii@gmail.com</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Nicole</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Hobbs</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>nicoldatalina.h@gmail.com</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Alyssa</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Bates</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>ambates@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Neal</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Edillon</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>nedillon@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Ella</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Mariveles</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>ellamariveles16@gmail.com</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Jeffrey</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>dr.jeffreycao@gmail.com</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Anabieza</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>jamesanabieza@icloud.com</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Prete</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>mattprete1967@gmail.com</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Jeip</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Geneblazo</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>jigblaze@gmail.com</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>santosfamily11@icloud.com</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Izzy</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Prete</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>izzyprete11@gmail.com</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Monzon</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>jose.monzon@hotmail.ca</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Prete</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>shawnaprete+1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Ray</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Recto</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>rayray780@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>markanddebra@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Angelbert</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>tenshi04@gmail.com</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Shawna</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Prete</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>shawnaprete@gmail.com</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Robin</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Espino</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>robinespino@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Keith</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Balante</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>kbalante@gmail.com</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>karin</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>pearce</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>karin-denise@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Nathan</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Davies</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>nathan@davies.tech</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Tracy</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Ray</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>tracyray@telus.net</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>lyla</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>rowe</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>lyla.rowe@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Cohen</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>jerry</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>rowe</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>jnrowe72@gmail.com</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Jon</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>jondeanestewart@gmail.com</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Paula Mae</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Magpayo</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>aluapeam@gmail.com</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Jason</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Snider</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>jason@rdlawyers.ca</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Robin</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Snider</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>robin.snider22@gmail.com</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Erin</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Bollinger</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>teawitherinb@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Tony</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Goutbeck</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>gouter@live.ca</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Erin</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Porodanuk</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>erin.porodanuk@gmail.com</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Marie-Astrid</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Detharet</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>mdetharet@cesd73.ca</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Brian</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Rubia</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>brianrubia@gmail.com</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Leanna</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Barillo</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>leanna.barillo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Mamac</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>paula.mamac@gmail.com</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Tan</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>victor.tan@gmail.com</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Sharleen</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Mamac</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>lacacapam@gmail.com</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Crooks</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>devin.crooks13@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Mary Ann</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Revosura</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>mayannrevosura@gmail.com</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Primery</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Munez</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>primererymunez@gmail.com</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Annissa</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Crooks</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>devin.crooks12@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Pizaarres</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>josepizaarres@gmail.com</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Dionalavo</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>janelle@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Franka</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Two</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>franka.two@gmail.com</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Porodnauk</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>steven.porodnauk@gmail.com</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Nicole</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Burkmar</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>nburkmar@gmail.com</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Ma Treshia Mai</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Mamac</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>treshia.mamac@gmail.com</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Devin</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Crooks</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>devincrooks@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Richter</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>richter_aaron@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Marvious</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>jennifer.marvoius@gmail.com</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Red_Deer.xlsx
+++ b/docs/downloads/Red_Deer.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D535"/>
+  <dimension ref="A1:D365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -919,17 +919,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Juk</t>
+          <t>Heykants</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>valnow+2@hotmail.com</t>
+          <t>heykantsadam@yahoo.ca</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -941,17 +941,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ayan</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kuon</t>
+          <t>Juk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>valnow+@hotmail.com</t>
+          <t>valnow+2@hotmail.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -963,17 +963,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ira</t>
+          <t>Ayan</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stark</t>
+          <t>Kuon</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>iras_ca@hotmail.com</t>
+          <t>valnow+@hotmail.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1007,17 +1007,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Joel</t>
+          <t>Morgann</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Luchsinger</t>
+          <t>Brewster</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>hdhobo+1@gmail.com</t>
+          <t>morgann.brewster03@gmail.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pelletier</t>
+          <t>Luchsinger</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>reddeercoaching@pickleplexclub.ca</t>
+          <t>hdhobo+1@gmail.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1051,17 +1051,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Joel</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Andrews</t>
+          <t>Pelletier</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>thscp@telusplanet.net</t>
+          <t>reddeercoaching@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Annette</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mcmillan</t>
+          <t>Andrews</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2moreau@telus.net</t>
+          <t>thscp@telusplanet.net</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1095,17 +1095,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Annette</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lim</t>
+          <t>Mcmillan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>noahalim@icloud.com</t>
+          <t>2moreau@telus.net</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1117,17 +1117,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Megan</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nederlof</t>
+          <t>Lim</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>megannederlof1@gmail.com</t>
+          <t>noahalim@icloud.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1139,17 +1139,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Desna</t>
+          <t>Megan</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Karunnyaka</t>
+          <t>Nederlof</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>kddisna@yahoo.com</t>
+          <t>megannederlof1@gmail.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1161,17 +1161,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Lesley</t>
+          <t>Desna</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Marriott</t>
+          <t>Karunnyaka</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>lesley_m13@yahoo.ca</t>
+          <t>kddisna@yahoo.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Arista</t>
+          <t>Lesley</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bouch</t>
+          <t>Marriott</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>bouchpa@gmail.com</t>
+          <t>lesley_m13@yahoo.ca</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1205,17 +1205,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pamela</t>
+          <t>Arista</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>Bouch</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>pamelajmiller138@gmail.com</t>
+          <t>bouchpa@gmail.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1227,17 +1227,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kelsie</t>
+          <t>Pamela</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Blackwell</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>kelsie@pickleplexclub.ca</t>
+          <t>pamelajmiller138@gmail.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1249,17 +1249,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sandra</t>
+          <t>Kelsie</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mackie</t>
+          <t>Blackwell</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>aaaa@gmail.com</t>
+          <t>kelsie@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1271,17 +1271,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Sandra</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wyntjes</t>
+          <t>Mackie</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>dylanwynjes@hotmail.com</t>
+          <t>aaaa@gmail.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1293,17 +1293,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Wyntjes</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>wilsonjp76@gmail.com</t>
+          <t>dylanwynjes@hotmail.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1315,17 +1315,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Townsend</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>julie@townsendelectrical.ca</t>
+          <t>wilsonjp76@gmail.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1337,17 +1337,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tommy jr 2</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Paquette</t>
+          <t>Townsend</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>anthony.paq269+2@gmail.com</t>
+          <t>julie@townsendelectrical.ca</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1359,17 +1359,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Doug</t>
+          <t>Tommy jr 2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DeWitt</t>
+          <t>Paquette</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>doug_dewitt@hotmail.com</t>
+          <t>anthony.paq269+2@gmail.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1425,17 +1425,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Dick</t>
+          <t>Patricia</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Feser</t>
+          <t>Lim</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>dickfeser@gmail.com</t>
+          <t>patricialim19@gmail.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1447,17 +1447,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Patricia</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lim</t>
+          <t>Blair</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>patricialim19@gmail.com</t>
+          <t>dmboard@telus.net</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1469,17 +1469,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alayne</t>
+          <t>Malika</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Farries</t>
+          <t>Yohan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>amfarries@me.com</t>
+          <t>yohansilba205@gmail.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1491,17 +1491,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Blair</t>
+          <t>Pochylko</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>dmboard@telus.net</t>
+          <t>lucas@andystrucksales.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1513,17 +1513,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Malika</t>
+          <t>Parry</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Yohan</t>
+          <t>Dyck</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>yohansilba205@gmail.com</t>
+          <t>donutm@telus.net</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1535,17 +1535,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pochylko</t>
+          <t>Lim</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>lucas@andystrucksales.com</t>
+          <t>bentholim@gmail.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1557,17 +1557,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Parry</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dyck</t>
+          <t>Townsend</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>donutm@telus.net</t>
+          <t>scott@townsendelectrical.ca</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1579,17 +1579,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lim</t>
+          <t>Lecompte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>bentholim@gmail.com</t>
+          <t>michellelecompte1@gmail.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1601,17 +1601,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Derrek</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Townsend</t>
+          <t>Halberson</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>scott@townsendelectrical.ca</t>
+          <t>derrekhalberson@gmail.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1623,17 +1623,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Derrek</t>
+          <t>Nikki</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Halberson</t>
+          <t>Lastname</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>derrekhalberson@gmail.com</t>
+          <t>chia-fray-1g@icloud.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1645,17 +1645,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Nikki</t>
+          <t>Red deer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Lastname</t>
+          <t>Accounting</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>chia-fray-1g@icloud.com</t>
+          <t>reddeeraccounting@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1667,17 +1667,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Red deer</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Monville</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>reddeeraccounting@pickleplexclub.ca</t>
+          <t>thomas@monvillelandscaping.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1689,17 +1689,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Monville</t>
+          <t>Swenson</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>thomas@monvillelandscaping.com</t>
+          <t>gregswenson04@gmail.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1711,17 +1711,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Kingsley</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Swenson</t>
+          <t>Grice</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>gregswenson04@gmail.com</t>
+          <t>grice_kingsley@hotmail.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1733,17 +1733,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Kingsley</t>
+          <t>Shayne</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Grice</t>
+          <t>Luchsinger</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>grice_kingsley@hotmail.com</t>
+          <t>hdhobo@gmail.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1755,17 +1755,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Doug</t>
+          <t>Antonthy</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Lemieux</t>
+          <t>Judd</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>djlemieux11@gmail.com</t>
+          <t>anthony.judd@ig.ca</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1777,17 +1777,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Shayne</t>
+          <t>Rick</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Luchsinger</t>
+          <t>Adie</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>hdhobo@gmail.com</t>
+          <t>hugo2196@proton.me</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1799,17 +1799,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Antonthy</t>
+          <t>Kris</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Judd</t>
+          <t>Krzysik</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>anthony.judd@ig.ca</t>
+          <t>kriskrzysik@hotmail.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1821,17 +1821,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Rick</t>
+          <t>Elena</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Adie</t>
+          <t>Durette</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>hugo2196@proton.me</t>
+          <t>ejdurett+1@gmail.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1843,17 +1843,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Kris</t>
+          <t>Branden</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Krzysik</t>
+          <t>Macdonald</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>kriskrzysik@hotmail.com</t>
+          <t>brandenmac@gmail.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1865,17 +1865,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Durette</t>
+          <t>Peden</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ejdurett+1@gmail.com</t>
+          <t>julieapeden@gmail.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1887,17 +1887,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Peden</t>
+          <t>Macpherson</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>julieapeden@gmail.com</t>
+          <t>ethanmac@yahoo.ca</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1909,17 +1909,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Steven</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Macpherson</t>
+          <t>Thomlison</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ethanmac@yahoo.ca</t>
+          <t>schrest+2@telusplanet.net</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1931,17 +1931,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Steven</t>
+          <t>Yannick</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Thomlison</t>
+          <t>Reid</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>schrest+2@telusplanet.net</t>
+          <t>reidroamer@gmail.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Yannick</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Reid</t>
+          <t>Bilo</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>reidroamer@gmail.com</t>
+          <t>avabee314@gmail.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1975,17 +1975,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ava</t>
+          <t>Axton</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bilo</t>
+          <t>Grutterink</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>avabee314@gmail.com</t>
+          <t>hjgrutterink+7@hotmail.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1997,17 +1997,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Axton</t>
+          <t>Debbie</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Grutterink</t>
+          <t>Salmon</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>hjgrutterink+7@hotmail.com</t>
+          <t>debesalmon@gmail.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2085,17 +2085,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Chay</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Kean</t>
+          <t>Feuser</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>bendover@airenet.com</t>
+          <t>chay_feuser@hotmail.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2107,17 +2107,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Merrill</t>
+          <t>Dwayne</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kean</t>
+          <t>Mcarthur</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>merrill@cherryhillauction.com</t>
+          <t>sands1@telusplanet.net</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2129,17 +2129,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Chay</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Feuser</t>
+          <t>Genereux</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>chay_feuser@hotmail.com</t>
+          <t>emgrose@telus.net</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2151,17 +2151,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Dwayne</t>
+          <t>Tony</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mcarthur</t>
+          <t>Judd</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>sands1@telusplanet.net</t>
+          <t>a_judd@live.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2173,17 +2173,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Genereux</t>
+          <t>Delaronde</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>emgrose@telus.net</t>
+          <t>melissa_delaronde@hotmail.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2195,17 +2195,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Annie</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Delaronde</t>
+          <t>Collins</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>melissa_delaronde@hotmail.com</t>
+          <t>annie.collins0319@gmail.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2217,17 +2217,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Annie</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Collins</t>
+          <t>Langard</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>annie.collins0319@gmail.com</t>
+          <t>jordanlangard@gmail.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2239,17 +2239,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Yapa</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Langard</t>
+          <t>Banbara</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>jordanlangard@gmail.com</t>
+          <t>yapa1@mail.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2261,17 +2261,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Yapa</t>
+          <t>Holly</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Banbara</t>
+          <t>Mundorf</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>yapa1@mail.com</t>
+          <t>theartturtle@gmail.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2283,17 +2283,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Holly</t>
+          <t>Helen</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Mundorf</t>
+          <t>Swanson</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>theartturtle@gmail.com</t>
+          <t>watercoursewaystudio@gmail.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2305,17 +2305,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Helen</t>
+          <t>Dom</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Swanson</t>
+          <t>Gomes</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>watercoursewaystudio@gmail.com</t>
+          <t>domgomesmedia@gmail.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2327,17 +2327,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Dom</t>
+          <t>Sau mei</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Gomes</t>
+          <t>Lam</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>domgomesmedia@gmail.com</t>
+          <t>lamsaumei510@gmail.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2349,19 +2349,15 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sau mei</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Lam</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>lamsaumei510@gmail.com</t>
-        </is>
-      </c>
+          <t>Pylypets</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -2371,15 +2367,19 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Frank</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Pylypets</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>Gallie</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>frank1gallie1@gmail.com</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -2389,19 +2389,15 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Frank</t>
+          <t>Nahum</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Gallie</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>frank1gallie1@gmail.com</t>
-        </is>
-      </c>
+          <t>Pinette</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -2411,15 +2407,19 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Nahum</t>
+          <t>Brenda</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Pinette</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
+          <t>Bale</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>bcalvin4@gmail.com</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -3943,17 +3943,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Dianne</t>
+          <t>Abe</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Gomes</t>
+          <t>Halverson</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>dianne.gomes1@gmail.com</t>
+          <t>colleen.abe+1@gmail.com</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -3965,17 +3965,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Jody</t>
+          <t>Dianne</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Muth</t>
+          <t>Gomes</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>gramadoes@gmail.com</t>
+          <t>dianne.gomes1@gmail.com</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -3987,17 +3987,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Eoin</t>
+          <t>Jody</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Wolfe</t>
+          <t>Muth</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>wolfeeion@gmail.com</t>
+          <t>gramadoes@gmail.com</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4009,15 +4009,19 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Clõy</t>
+          <t>Eoin</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Jones</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr"/>
+          <t>Wolfe</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>wolfeeion@gmail.com</t>
+        </is>
+      </c>
       <c r="D178" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4027,12 +4031,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Brielle</t>
+          <t>Clõy</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Tweten</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -4045,12 +4049,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Bennett</t>
+          <t>Brielle</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Tweten</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -4063,12 +4067,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Teagan</t>
+          <t>Bennett</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Coulter</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -4081,7 +4085,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Kinley</t>
+          <t>Teagan</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4099,12 +4103,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>McKinley</t>
+          <t>Kinley</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Coulter</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -4117,12 +4121,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Maris</t>
+          <t>McKinley</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Epp</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -4135,12 +4139,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Maris</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Polachek</t>
+          <t>Epp</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -4153,12 +4157,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Tweten</t>
+          <t>Polachek</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -4171,19 +4175,15 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Hunter</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Krywik</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>cad.support.contractors@gmail.com</t>
-        </is>
-      </c>
+          <t>Tweten</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4193,15 +4193,19 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Kayla</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Lane</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr"/>
+          <t>Krywik</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>cad.support.contractors@gmail.com</t>
+        </is>
+      </c>
       <c r="D188" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4211,12 +4215,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Joel</t>
+          <t>Kayla</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Peterman</t>
+          <t>Lane</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -4229,12 +4233,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Chase</t>
+          <t>Joel</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Girletz</t>
+          <t>Peterman</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -4247,7 +4251,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Stratten</t>
+          <t>Chase</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4265,12 +4269,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Gavin</t>
+          <t>Stratten</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Girletz</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -4283,12 +4287,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Gavin</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Kosola</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -4301,12 +4305,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Danté</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Kosola</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -4319,12 +4323,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Brent</t>
+          <t>Danté</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -4337,12 +4341,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Rowyn</t>
+          <t>Brent</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Girletz</t>
+          <t>Young</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -4355,12 +4359,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Sheldon</t>
+          <t>Rowyn</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Girletz</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -4373,12 +4377,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Mackenzie</t>
+          <t>Sheldon</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Differenz</t>
+          <t>Lane</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -4391,12 +4395,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Quinn</t>
+          <t>Mackenzie</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Differenz</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -4409,12 +4413,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Vera</t>
+          <t>Quinn</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Kosola</t>
+          <t>Lane</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -4427,19 +4431,15 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Clint</t>
+          <t>Vera</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Buswell</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>clintbuswell@gmail.com</t>
-        </is>
-      </c>
+          <t>Kosola</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4449,7 +4449,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Rebeca</t>
+          <t>Clint</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>rebecabuswell@gmail.com</t>
+          <t>clintbuswell@gmail.com</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -4471,17 +4471,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Rebeca</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Brownell</t>
+          <t>Buswell</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>emersonbrownell@gmail.com</t>
+          <t>rebecabuswell@gmail.com</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -4493,17 +4493,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Carla</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Mccrae</t>
+          <t>Brownell</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>carlanmccrae@gmail.com</t>
+          <t>emersonbrownell@gmail.com</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -4515,17 +4515,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Carla</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Brownell</t>
+          <t>Mccrae</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>brownel+@telus.net</t>
+          <t>carlanmccrae@gmail.com</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -4537,17 +4537,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Treu</t>
+          <t>Wiebe</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>ltreu@telus.net</t>
+          <t>rileywiebe@gmail.com</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -4559,15 +4559,19 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Kang</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr"/>
+          <t>Brownell</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>brownel+@telus.net</t>
+        </is>
+      </c>
       <c r="D207" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4577,15 +4581,19 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Beau</t>
+          <t>Colleen</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Becker</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr"/>
+          <t>Githu</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>colleengithu@gmail.com</t>
+        </is>
+      </c>
       <c r="D208" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4595,17 +4603,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Kang</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Huang</t>
+          <t>Treu</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>andrehuang74@gmail.com</t>
+          <t>ltreu@telus.net</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -4617,12 +4625,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Li Juan</t>
+          <t>Kang</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Tong</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -4635,19 +4643,15 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>artur</t>
+          <t>Beau</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Hayrepetyan</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>hayreptyan1115@gmail.com</t>
-        </is>
-      </c>
+          <t>Becker</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4657,15 +4661,19 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Kang</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Sopkow</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr"/>
+          <t>Huang</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>andrehuang74@gmail.com</t>
+        </is>
+      </c>
       <c r="D212" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4675,12 +4683,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Emersyn</t>
+          <t>Li Juan</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Spina</t>
+          <t>Tong</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -4693,15 +4701,19 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Ruth</t>
+          <t>artur</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Howley</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr"/>
+          <t>Hayrepetyan</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>hayreptyan1115@gmail.com</t>
+        </is>
+      </c>
       <c r="D214" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4711,12 +4723,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Camryn</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Spina</t>
+          <t>Sopkow</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -4729,12 +4741,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Piper</t>
+          <t>Emersyn</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Watt</t>
+          <t>Spina</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -4747,12 +4759,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Ruth</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Schurek</t>
+          <t>Howley</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -4765,12 +4777,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Adelyn</t>
+          <t>Camryn</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Visser</t>
+          <t>Spina</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -4783,12 +4795,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Harper</t>
+          <t>Piper</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Harnett</t>
+          <t>Watt</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -4801,12 +4813,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Blake</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Watt</t>
+          <t>Schurek</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -4819,12 +4831,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Renn</t>
+          <t>Adelyn</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Schurek</t>
+          <t>Visser</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -4837,12 +4849,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Lauren</t>
+          <t>Harper</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Sopkow</t>
+          <t>Harnett</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -4855,7 +4867,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Brynn</t>
+          <t>Blake</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -4873,7 +4885,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Jayde</t>
+          <t>Renn</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -4891,7 +4903,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Kate</t>
+          <t>Lauren</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -4909,12 +4921,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Makenna</t>
+          <t>Brynn</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Watt</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -4927,12 +4939,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Lainey</t>
+          <t>Jayde</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Klassen</t>
+          <t>Schurek</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -4945,12 +4957,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Kate</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Klassen</t>
+          <t>Sopkow</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -4963,12 +4975,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Bryn</t>
+          <t>Makenna</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -4981,7 +4993,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Lainey</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -4999,19 +5011,15 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Bailey</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>kirstenwestberg+111@gmail.com</t>
-        </is>
-      </c>
+          <t>Klassen</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -5021,12 +5029,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Abbiegale</t>
+          <t>Bryn</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Hunter</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -5039,19 +5047,15 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Sandi</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>O'Brien</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>sandals_84@hotmail.com</t>
-        </is>
-      </c>
+          <t>Klassen</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -5061,15 +5065,19 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Bbbb</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Dorbyk</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr"/>
+          <t>Bailey</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>kirstenwestberg+111@gmail.com</t>
+        </is>
+      </c>
       <c r="D234" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -5079,7 +5087,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Paxton</t>
+          <t>Abbiegale</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5097,15 +5105,19 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Madison</t>
+          <t>Talon</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Judd</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr"/>
+          <t>O'Brien</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>talonobrien09@outlook.com</t>
+        </is>
+      </c>
       <c r="D236" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -5115,15 +5127,19 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>Sandi</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Debogorski</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr"/>
+          <t>O'Brien</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>sandals_84@hotmail.com</t>
+        </is>
+      </c>
       <c r="D237" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -5133,12 +5149,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Tenley</t>
+          <t>Bbbb</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>Dorbyk</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -5151,12 +5167,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>Paxton</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Blum</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -5169,12 +5185,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>Madison</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Olson</t>
+          <t>Judd</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -5187,12 +5203,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Crystal</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Webber</t>
+          <t>Debogorski</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -5205,7 +5221,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Alyvia</t>
+          <t>Tenley</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5223,12 +5239,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Adriana</t>
+          <t>Aiden</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>VanLochem</t>
+          <t>Blum</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -5241,12 +5257,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Trevor</t>
+          <t>Aiden</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Vickery</t>
+          <t>Olson</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -5259,12 +5275,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Hailey</t>
+          <t>Crystal</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>Webber</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -5277,12 +5293,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Alyvia</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Ayuno</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -5295,12 +5311,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Jax</t>
+          <t>Adriana</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>VanLochem</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -5313,12 +5329,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Tessa</t>
+          <t>Trevor</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>Vickery</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -5331,12 +5347,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Josiah</t>
+          <t>Hailey</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Oickle</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -5349,12 +5365,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Dion</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Krause</t>
+          <t>Ayuno</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -5367,12 +5383,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Vienne</t>
+          <t>Jax</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Wilkening</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -5385,12 +5401,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Jaykob</t>
+          <t>Tessa</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Oickle</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -5403,12 +5419,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Josiah</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>VanLochem</t>
+          <t>Oickle</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -5421,12 +5437,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Dion</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Blum</t>
+          <t>Krause</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -5439,12 +5455,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Gage</t>
+          <t>Vienne</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Liebig</t>
+          <t>Wilkening</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -5457,12 +5473,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Jaykob</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>Oickle</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -5475,12 +5491,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>VanLochem</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -5493,12 +5509,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>AJ</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Celis</t>
+          <t>Blum</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -5511,12 +5527,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Adilynn</t>
+          <t>Gage</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Whiles</t>
+          <t>Liebig</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -5529,12 +5545,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Bovey</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -5547,12 +5563,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Taya</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Ferguson</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -5565,12 +5581,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>AJ</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Glimsdale</t>
+          <t>Celis</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -5583,12 +5599,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Braiden</t>
+          <t>Adilynn</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Michnik</t>
+          <t>Whiles</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -5601,12 +5617,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>VanLochem</t>
+          <t>Bovey</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -5619,12 +5635,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Liliam</t>
+          <t>Taya</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Marinero</t>
+          <t>Ferguson</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -5637,12 +5653,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Richelle</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Hansen</t>
+          <t>Glimsdale</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -5655,12 +5671,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Braiden</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Judd</t>
+          <t>Michnik</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -5673,12 +5689,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Seth</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Gill</t>
+          <t>VanLochem</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -5691,12 +5707,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Liliam</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Bousquet</t>
+          <t>Marinero</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -5709,12 +5725,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Richelle</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Hansen</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
@@ -5727,12 +5743,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Michnik</t>
+          <t>Judd</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -5745,12 +5761,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Seth</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Vickery</t>
+          <t>Gill</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -5763,12 +5779,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Kolton</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Balaneski</t>
+          <t>Bousquet</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -5781,12 +5797,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Sophia</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Judd</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -5799,12 +5815,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>MacKenzie</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Michnik</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -5817,12 +5833,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Brooks</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Hansen</t>
+          <t>Vickery</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -5835,12 +5851,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>Kolton</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Webber</t>
+          <t>Balaneski</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
@@ -5853,12 +5869,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Karston</t>
+          <t>Sophia</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Loehndorf</t>
+          <t>Judd</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -5871,12 +5887,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Criszel</t>
+          <t>MacKenzie</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Maraon</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -5889,12 +5905,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Franko</t>
+          <t>Brooks</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Hansen</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -5907,12 +5923,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Connor</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Michnik</t>
+          <t>Webber</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
@@ -5925,12 +5941,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Karston</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Loehndorf</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
@@ -5943,12 +5959,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Burke</t>
+          <t>Criszel</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Maraon</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -5961,12 +5977,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Franko</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Liebig</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -5979,12 +5995,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Ivy</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Bovey</t>
+          <t>Michnik</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -5997,12 +6013,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Dore</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -6015,12 +6031,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Bowen</t>
+          <t>Burke</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -6033,12 +6049,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Steven</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Ruppert</t>
+          <t>Liebig</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -6051,12 +6067,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Coen</t>
+          <t>Ivy</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Hansen</t>
+          <t>Bovey</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
@@ -6069,12 +6085,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Bakker</t>
+          <t>Dore</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
@@ -6087,12 +6103,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Katelin</t>
+          <t>Bowen</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Friesen</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
@@ -6105,12 +6121,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Devin</t>
+          <t>Steven</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Holzer</t>
+          <t>Ruppert</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
@@ -6123,12 +6139,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Dean</t>
+          <t>Coen</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Lunde</t>
+          <t>Hansen</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
@@ -6141,19 +6157,15 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Brenda</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Wyntjes</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>pipercreekpetresort@outlook.com</t>
-        </is>
-      </c>
+          <t>Bakker</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6163,12 +6175,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Brady</t>
+          <t>Katelin</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Maaskant</t>
+          <t>Friesen</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
@@ -6181,12 +6193,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Christ</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Keumoe</t>
+          <t>Holzer</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
@@ -6199,15 +6211,19 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Pedro</t>
+          <t>Karissa</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Bazzan</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr"/>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>shawnmain@me.com</t>
+        </is>
+      </c>
       <c r="D297" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6217,12 +6233,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Linden</t>
+          <t>Dean</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Skrodolis</t>
+          <t>Lunde</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
@@ -6235,15 +6251,19 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Zylah</t>
+          <t>Brenda</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Bizimana</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr"/>
+          <t>Wyntjes</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>pipercreekpetresort@outlook.com</t>
+        </is>
+      </c>
       <c r="D299" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6253,19 +6273,15 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Danielle</t>
+          <t>Brady</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Haessel</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>danielleparker482@hotmail.com</t>
-        </is>
-      </c>
+          <t>Maaskant</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6275,12 +6291,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>Christ</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Skrodolis</t>
+          <t>Keumoe</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
@@ -6293,19 +6309,15 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Craig</t>
+          <t>Pedro</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Gomez</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>craig.shawn.gomez@gmail.com</t>
-        </is>
-      </c>
+          <t>Bazzan</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6315,19 +6327,15 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Linden</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Gizikoff</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>info@lepagephc.ca</t>
-        </is>
-      </c>
+          <t>Skrodolis</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6337,19 +6345,15 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Zylah</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Yaholkoski</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>jason@fitnessinthehome.com</t>
-        </is>
-      </c>
+          <t>Bizimana</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6359,15 +6363,19 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Ellie</t>
+          <t>Danielle</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Glover</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr"/>
+          <t>Haessel</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>danielleparker482@hotmail.com</t>
+        </is>
+      </c>
       <c r="D305" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6377,12 +6385,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Wendy</t>
+          <t>Connor</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Glover</t>
+          <t>Skrodolis</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
@@ -6395,15 +6403,19 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Craig</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Glover</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr"/>
+          <t>Gomez</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>craig.shawn.gomez@gmail.com</t>
+        </is>
+      </c>
       <c r="D307" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6413,17 +6425,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Shakil</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Papel</t>
+          <t>Gizikoff</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>sk17papel@gmail.com</t>
+          <t>info@lepagephc.ca</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -6435,12 +6447,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Alyssa</t>
+          <t>Ellie</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Sherwin</t>
+          <t>Glover</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
@@ -6453,12 +6465,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Seth</t>
+          <t>Wendy</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Gill</t>
+          <t>Glover</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
@@ -6471,12 +6483,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Jai-Li</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Harvey</t>
+          <t>Glover</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
@@ -6489,15 +6501,19 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Raine</t>
+          <t>Shakil</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Joson</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr"/>
+          <t>Papel</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>sk17papel@gmail.com</t>
+        </is>
+      </c>
       <c r="D312" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6507,12 +6523,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Isaac</t>
+          <t>Alyssa</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Park</t>
+          <t>Sherwin</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
@@ -6525,12 +6541,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Fisher</t>
+          <t>Seth</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Dunphy</t>
+          <t>Gill</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
@@ -6543,12 +6559,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Ayden</t>
+          <t>Jai-Li</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Quinlan</t>
+          <t>Harvey</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
@@ -6561,12 +6577,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>Raine</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>Joson</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
@@ -6579,12 +6595,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Marah</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Dunphy</t>
+          <t>Park</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
@@ -6597,12 +6613,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Fisher</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Fleck</t>
+          <t>Dunphy</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
@@ -6615,12 +6631,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Ayden</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>McRae</t>
+          <t>Quinlan</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
@@ -6633,19 +6649,15 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Hanna</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Safron</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>hannasafron@icloud.com</t>
-        </is>
-      </c>
+          <t>Kennedy</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6655,12 +6667,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Marah</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Howard</t>
+          <t>Dunphy</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
@@ -6673,19 +6685,15 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Mila</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Haynes</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>cristinabagundol@yahoo.com</t>
-        </is>
-      </c>
+          <t>Fleck</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6695,12 +6703,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Robberstad</t>
+          <t>McRae</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
@@ -6713,15 +6721,19 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Shayne</t>
+          <t>Hanna</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Malsbury</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr"/>
+          <t>Safron</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>hannasafron@icloud.com</t>
+        </is>
+      </c>
       <c r="D324" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6731,12 +6743,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>McClelland</t>
+          <t>Howard</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
@@ -6749,15 +6761,19 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Larry</t>
+          <t>Mila</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Vetter</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr"/>
+          <t>Haynes</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>cristinabagundol@yahoo.com</t>
+        </is>
+      </c>
       <c r="D326" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6767,12 +6783,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Vetter</t>
+          <t>Robberstad</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
@@ -6785,12 +6801,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Shayne</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Fuchs</t>
+          <t>Malsbury</t>
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
@@ -6803,15 +6819,19 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Meyer</t>
+          <t>laura</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Fuchs</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr"/>
+          <t>edwards</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>alfedwards58@gmail.com</t>
+        </is>
+      </c>
       <c r="D329" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6821,19 +6841,15 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Serenna</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Constable</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>reddeer@bredin.ca</t>
-        </is>
-      </c>
+          <t>McClelland</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6843,19 +6859,15 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Carter</t>
+          <t>Larry</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Proft</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>carter.proft@iaprivatewealth.ca</t>
-        </is>
-      </c>
+          <t>Vetter</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6865,19 +6877,15 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Sakthi</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Aenugula</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>sakthiprasanth.aenugula@novachem.com</t>
-        </is>
-      </c>
+          <t>Vetter</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6887,12 +6895,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Nikki</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Januszewski</t>
+          <t>Fuchs</t>
         </is>
       </c>
       <c r="C333" t="inlineStr"/>
@@ -6905,12 +6913,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Buffy</t>
+          <t>Meyer</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Robblee</t>
+          <t>Fuchs</t>
         </is>
       </c>
       <c r="C334" t="inlineStr"/>
@@ -6923,15 +6931,19 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Zoey</t>
+          <t>Serenna</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Januszewski</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr"/>
+          <t>Constable</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>reddeer@bredin.ca</t>
+        </is>
+      </c>
       <c r="D335" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6941,15 +6953,19 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Carter</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>McPeek</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr"/>
+          <t>Proft</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>carter.proft@iaprivatewealth.ca</t>
+        </is>
+      </c>
       <c r="D336" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6959,15 +6975,19 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Ella</t>
+          <t>Sakthi</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Januszewski</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr"/>
+          <t>Aenugula</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>sakthiprasanth.aenugula@novachem.com</t>
+        </is>
+      </c>
       <c r="D337" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6977,12 +6997,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Barb</t>
+          <t>Nikki</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Pfannmueler</t>
+          <t>Januszewski</t>
         </is>
       </c>
       <c r="C338" t="inlineStr"/>
@@ -6995,12 +7015,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Adyson</t>
+          <t>Buffy</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Trepanier</t>
+          <t>Robblee</t>
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
@@ -7013,12 +7033,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Zoey</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Trepanier</t>
+          <t>Januszewski</t>
         </is>
       </c>
       <c r="C340" t="inlineStr"/>
@@ -7031,12 +7051,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Trepanier</t>
+          <t>McPeek</t>
         </is>
       </c>
       <c r="C341" t="inlineStr"/>
@@ -7049,19 +7069,15 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Megan &amp; John</t>
+          <t>Ella</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Heinen</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>maheinen84@gmail.com</t>
-        </is>
-      </c>
+          <t>Januszewski</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7071,12 +7087,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Barb</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Cote</t>
+          <t>Pfannmueler</t>
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
@@ -7089,12 +7105,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Jayda</t>
+          <t>Adyson</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Differenz</t>
+          <t>Trepanier</t>
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
@@ -7107,19 +7123,15 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>julien</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>kelly</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>kellyseamus=+1@hotmail.com</t>
-        </is>
-      </c>
+          <t>Trepanier</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7129,19 +7141,15 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Davison</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>jldav78@gmail.com</t>
-        </is>
-      </c>
+          <t>Trepanier</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7151,17 +7159,17 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Kaitlin</t>
+          <t>Megan &amp; John</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Meier</t>
+          <t>Heinen</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>kmeier@pivotalcpa.ca</t>
+          <t>maheinen84@gmail.com</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -7173,19 +7181,15 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Tristin</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Brisbois</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>tristin.brisbois@reddeer.ca</t>
-        </is>
-      </c>
+          <t>Cote</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7195,19 +7199,15 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Charlene</t>
+          <t>Jayda</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Parcels</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>ashley_parcels21+1@hotmail.com</t>
-        </is>
-      </c>
+          <t>Differenz</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7217,17 +7217,17 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>julien</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Escobar</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>escobar8765@gmail.com</t>
+          <t>kellyseamus=+1@hotmail.com</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -7239,17 +7239,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Alison</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Davison</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>areweeoran@gmail.com</t>
+          <t>jldav78@gmail.com</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -7261,17 +7261,17 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Cinzia</t>
+          <t>Kaitlin</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Gaudelli</t>
+          <t>Meier</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>cinzia.gaudelli@gmial.com</t>
+          <t>kmeier@pivotalcpa.ca</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -7283,17 +7283,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Amy</t>
+          <t>Tristin</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Musuronchan</t>
+          <t>Brisbois</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>clientcare@trilliantrealty.ca</t>
+          <t>tristin.brisbois@reddeer.ca</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -7305,17 +7305,17 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Jaclyn</t>
+          <t>leslie</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Parcels</t>
+          <t>wright</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>beandeane21@gmail.com</t>
+          <t>leslie0985@hotmail.com</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -7327,19 +7327,15 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Jeff</t>
+          <t>Hunter</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Dell</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>jeffgdell@gmail.com</t>
-        </is>
-      </c>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7349,19 +7345,15 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Fatima</t>
+          <t>Seija</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Hilario</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>f.hilario1997@gmail.com</t>
-        </is>
-      </c>
+          <t>Worth</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7371,19 +7363,15 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Ashley</t>
+          <t>Elias</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Parcels</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>ashley_parcels21@hotmail.com</t>
-        </is>
-      </c>
+          <t>Worth</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7393,17 +7381,17 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Danny</t>
+          <t>Khryzzia Kaye</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Benfeito</t>
+          <t>Mendio</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>dannybenfeito929@hotmail.com</t>
+          <t>mendio.kaye@gmail.com</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -7415,19 +7403,15 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Cohen</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>lanemenard@yahoo.com</t>
-        </is>
-      </c>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7437,17 +7421,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Simon</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Escobar</t>
+          <t>Snider</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>sbescobar@outlook.com</t>
+          <t>jason@rdlawyers.ca</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -7459,19 +7443,15 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Kiril</t>
+          <t>Quinn</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Serbin</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>kirilkse@gmail.com</t>
-        </is>
-      </c>
+          <t>Schmaltz</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7481,19 +7461,15 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Maksym</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Mamonov</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>vkmra@gmail.com</t>
-        </is>
-      </c>
+          <t>Kilbreath</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7503,19 +7479,15 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Jovi</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Barnabe</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>lbarnabe432@gmail.com</t>
-        </is>
-      </c>
+          <t>Kilbreath</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7525,19 +7497,15 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Frankie</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Cummings</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>fbradley@fibreop.ca</t>
-        </is>
-      </c>
+          <t>Kilbreath</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7547,3744 +7515,16 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Kade</t>
+          <t>Rio</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Doyle</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>kadepdoyle@gmail.com</t>
-        </is>
-      </c>
+          <t>Kilbreath</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>Aleigha</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>Seguin</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>aleighaseguin@gmail.com</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>Anthony</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>Daniel</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>anthony.daniel07@icloud.com</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>Abby</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>Schetszle</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>aschetza@gmail.com</t>
-        </is>
-      </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>Kade</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>Garritty</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>kadegarrity16@gmail.com</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>Pat</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>Garritty</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>pat@tirlliantreality.ca</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>Anna</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>Yuen</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>annayuen@nanjing-school.com</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>Rian</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>Morin</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>rian2003morin@gmail.com</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>Gianfranco Miguel</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>Quiballo</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>gianquiballo.rpmmc@gmail.com</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>Garry</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>Lightbrown</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>glightbrown1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>Madison</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>Caine</t>
-        </is>
-      </c>
-      <c r="C375" t="inlineStr">
-        <is>
-          <t>madisonlcaine@gmail.com</t>
-        </is>
-      </c>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>leslie</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>wright</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>leslie0985@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>Natalya</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>Agafomov</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>natase29@msn.com</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>serozho</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>agafonon</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>serozhoagafonon@gmail.com</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>sergeui</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>agafonod</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>matase29+1@msn.com</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>Hopp</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>kristen@hopp.ca</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>Fraser</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr">
-        <is>
-          <t>fraser211@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>Teigan</t>
-        </is>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>McAuley</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>teigs100770@gmail.com</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>Dave</t>
-        </is>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>Macdermid</t>
-        </is>
-      </c>
-      <c r="C383" t="inlineStr">
-        <is>
-          <t>dave.macdermid@novachem.com</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>Hanz Izaac</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>Villanueva</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>hanzvillanueva@yahoo.com</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>Shane</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>Amundson</t>
-        </is>
-      </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>shane97a@icloud.com</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>Arturo</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>Raynoso</t>
-        </is>
-      </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>arturo.raynoso@gmail.com</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>Lorie</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>Fritz</t>
-        </is>
-      </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>lorifritz03@gmail.com</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>Ejiro</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>Oghenovo</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>oghenovosion@gmail.com</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>Oosterhoff</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>aoosterhoff1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>Jackie</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>Hofseth</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>jackie.hofseth@novachem.com</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>Gary</t>
-        </is>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>Murray</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>gary.murray@novachem.com</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>taylor.mitchell.green@gmail.com</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>Gerald</t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>Alexander</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>gerladalexander@shaw.ca</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>Zengshan</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>Gui</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>gui_jason@yahoo.ca</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>Yash</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>Kapil</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>yashkapil@novachem.com</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>Alex</t>
-        </is>
-      </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>Boyer</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>alex.d.boyer@gmail.com</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>Joel</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>Varghese</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>joelvarghesecanada@gmail.com</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>Sergio</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>Mojica</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>sergiomojica@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>Jason</t>
-        </is>
-      </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>Liptak</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>jason.liptak@novachem.com</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>Trent</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>lotgreen@hotmail.ca</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>Juan</t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>Ramirez</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>juan.ramirez@novachem.com</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>Connor</t>
-        </is>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>Einhorn</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>ceinhorn9@gmail.com</t>
-        </is>
-      </c>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>Amber</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>Sesak</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>ambersesak06@outlook.com</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>Tone</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>angtone@shaw.ca</t>
-        </is>
-      </c>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>Mark</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>Visser</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>blackpanther_26@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>Murray</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>Einhorn</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>meinhorn@shaw.ca</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>Steve</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>Frey</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>stvfrey2@gmail.com</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>Carrie</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>Turney</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>carrie.sue15@gmail.com</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>Brooklynn</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>brookfritz1993@gmail.com</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>Marceno</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>Nembhard</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>marceno.nembhard@gmail.com</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>Juliet</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>Mojica</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>jumojicabarboza@gmail.com</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>Vincent</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>Soong</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>vincentsoong@yahoo.com</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>Andrew</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>Mojica</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>ammbsx@gmail.com</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>Sunni</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>Yeow</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>sunni@createmethod.com</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>Tutu</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>H.</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>tutuyyc@gmail.com</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>Doofus</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>Cheng</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>sundayrosenine9@gmail.com</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>Adlina</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>Yeow</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>adlina@createmethod.com</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>Fernanda</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>Mojica</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>fernandamojicanoriega2007@gmail.com</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>Jolly</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>Hilay</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>jaih09@yahoo.com</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>Teryn</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>Chan</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>terynchan@yahoo.com</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>Gordon</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>Chan</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>gor.cha@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>Jackson</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>Spady</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>jacksonkspady@gmail.com</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>Merric</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>Roe</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>merricroe@icloud.com</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>Abe</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>Halvorsen</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>faberconstruction.abe@gmail.com</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>Kayla</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>Hebert</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>kayla.c.harrison@gmail.com</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>Ava</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>Spady</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>avaspady@gmail.com</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>Elizabeth</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>Wong</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>wong.liza24@gmail.com</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>Emma</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>Lacroix</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>emmalacroix834@gmail.com</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>Edgar</t>
-        </is>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>Herman</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>edgarhermanm@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>Robert</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>Lauze</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>robert.lauze16@gmail.com</t>
-        </is>
-      </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>Shelley</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>Lauze</t>
-        </is>
-      </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>shelley.lauze1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>Hunter</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>Frank</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>Young</t>
-        </is>
-      </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>borodoc13@gmail.com</t>
-        </is>
-      </c>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>chris</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>lewis</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>clewis@cjcedm.ca</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>vera</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>allen</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>lallen5+1@shaw.ca</t>
-        </is>
-      </c>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>linda</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>allen</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>lallen5@shaw.ca</t>
-        </is>
-      </c>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>Emily</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>Uebell</t>
-        </is>
-      </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>etuebell@gmail.com</t>
-        </is>
-      </c>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>Kristin</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>Quinn</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>kirstin.quinn23@gmail.com</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>Anita</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>Lode</t>
-        </is>
-      </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t>nitz.lobe@gmail.com</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>Sou</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>Hassan</t>
-        </is>
-      </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>souad.hassan992@gmail.com</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>Kaitlyn</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>Blaire</t>
-        </is>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>kaitlynblaire22@icloud.com</t>
-        </is>
-      </c>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>Alexandra</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>Hobbs</t>
-        </is>
-      </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>alekhobbs@gmail.com</t>
-        </is>
-      </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>Caroline</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>Panteluk</t>
-        </is>
-      </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>panteluk@shaw.ca</t>
-        </is>
-      </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>Mario</t>
-        </is>
-      </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>Gallant</t>
-        </is>
-      </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>mario.gallant@icloud.com</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>Juila</t>
-        </is>
-      </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>Vrotla</t>
-        </is>
-      </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>julia.vrotla@gmail.com</t>
-        </is>
-      </c>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>Iryna</t>
-        </is>
-      </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>Dinou</t>
-        </is>
-      </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>iryna.dinou@gmail.com</t>
-        </is>
-      </c>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>Emma</t>
-        </is>
-      </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>belich</t>
-        </is>
-      </c>
-      <c r="C447" t="inlineStr">
-        <is>
-          <t>emmabelich94@gmail.com</t>
-        </is>
-      </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>Rod</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>Dand</t>
-        </is>
-      </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>rcdand@shaw.ca</t>
-        </is>
-      </c>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>Will</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>Fierro</t>
-        </is>
-      </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>fierro1007@gmail.com</t>
-        </is>
-      </c>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>Chan</t>
-        </is>
-      </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>joechan3@gmail.com</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>Joan</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>Skiba</t>
-        </is>
-      </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>jskiba1@telus.net</t>
-        </is>
-      </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>Emree</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>Hart</t>
-        </is>
-      </c>
-      <c r="C452" t="inlineStr">
-        <is>
-          <t>meaghart@gmail.com</t>
-        </is>
-      </c>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>Liam</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>Lundmark</t>
-        </is>
-      </c>
-      <c r="C453" t="inlineStr">
-        <is>
-          <t>liam.lime35@gmail.com</t>
-        </is>
-      </c>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>Bob</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>Edwards</t>
-        </is>
-      </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>rcedwards58@gmail.com</t>
-        </is>
-      </c>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>Archer</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>Martin</t>
-        </is>
-      </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>hotsauceboss97@icloud.com</t>
-        </is>
-      </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>Atlas</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>Phadilla</t>
-        </is>
-      </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>tweetaaron+1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>Garry</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>Macintosh</t>
-        </is>
-      </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>macintoshgarry@gmail.com</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>Fierro</t>
-        </is>
-      </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>nicegmoreno@gmail.com</t>
-        </is>
-      </c>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>Abby</t>
-        </is>
-      </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>Holland</t>
-        </is>
-      </c>
-      <c r="C459" t="inlineStr">
-        <is>
-          <t>abby.holland@gmail.com</t>
-        </is>
-      </c>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>Snider</t>
-        </is>
-      </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>snider.jason@gmail.com</t>
-        </is>
-      </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>Ryan</t>
-        </is>
-      </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>Fox</t>
-        </is>
-      </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>fox60113@gmail.com</t>
-        </is>
-      </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>Clayton</t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>Watmough</t>
-        </is>
-      </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>claytonw@gibsonsbuilding.com</t>
-        </is>
-      </c>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>Jaycob</t>
-        </is>
-      </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>Ocol</t>
-        </is>
-      </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>jaycobalverto2@gmail.com</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>Richard</t>
-        </is>
-      </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>Helfmann</t>
-        </is>
-      </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>richardhelfmann@gmail.com</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>Sai Srivibhav</t>
-        </is>
-      </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>Swayampakula</t>
-        </is>
-      </c>
-      <c r="C465" t="inlineStr">
-        <is>
-          <t>chaitusvk@gmail.com</t>
-        </is>
-      </c>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>Seija</t>
-        </is>
-      </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>Worth</t>
-        </is>
-      </c>
-      <c r="C466" t="inlineStr"/>
-      <c r="D466" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>Elias</t>
-        </is>
-      </c>
-      <c r="B467" t="inlineStr">
-        <is>
-          <t>Worth</t>
-        </is>
-      </c>
-      <c r="C467" t="inlineStr"/>
-      <c r="D467" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>Justin</t>
-        </is>
-      </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>Derrick</t>
-        </is>
-      </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>jderrick921@gmail.com</t>
-        </is>
-      </c>
-      <c r="D468" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>Frances</t>
-        </is>
-      </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>Rovero</t>
-        </is>
-      </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>francesrovero45@gmail.com</t>
-        </is>
-      </c>
-      <c r="D469" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>John</t>
-        </is>
-      </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>Rovero</t>
-        </is>
-      </c>
-      <c r="C470" t="inlineStr">
-        <is>
-          <t>jvcrovero01@gmail.com</t>
-        </is>
-      </c>
-      <c r="D470" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>WAYNE</t>
-        </is>
-      </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>PANSEGRAM</t>
-        </is>
-      </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>wayne@topshelfarena.com</t>
-        </is>
-      </c>
-      <c r="D471" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>Jay</t>
-        </is>
-      </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>Palalon</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>daryljay1985@gmail.com</t>
-        </is>
-      </c>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>Jason</t>
-        </is>
-      </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>Biondo</t>
-        </is>
-      </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>jbiondodc@gmail.com</t>
-        </is>
-      </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>Rhenz</t>
-        </is>
-      </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>Viterbo</t>
-        </is>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>rhenzgabriel@gmail.com</t>
-        </is>
-      </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>quinn</t>
-        </is>
-      </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>whitecotton</t>
-        </is>
-      </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>mattwhitecotton+1@shaw.ca</t>
-        </is>
-      </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>london</t>
-        </is>
-      </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>adcock</t>
-        </is>
-      </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>mattwhitecotton+4@shaw.ca</t>
-        </is>
-      </c>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>cayson</t>
-        </is>
-      </c>
-      <c r="B477" t="inlineStr">
-        <is>
-          <t>waddell</t>
-        </is>
-      </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>mattwhitecotton+2@shaw.ca</t>
-        </is>
-      </c>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>devyn</t>
-        </is>
-      </c>
-      <c r="B478" t="inlineStr">
-        <is>
-          <t>whitecotton</t>
-        </is>
-      </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>mattwhitecotton+5@shaw.ca</t>
-        </is>
-      </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>Khryzzia Kaye</t>
-        </is>
-      </c>
-      <c r="B479" t="inlineStr">
-        <is>
-          <t>Mendio</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>mendio.kaye@gmail.com</t>
-        </is>
-      </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-      <c r="B480" t="inlineStr">
-        <is>
-          <t>McCuaig</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>mccuaigranch@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>Ines</t>
-        </is>
-      </c>
-      <c r="B481" t="inlineStr">
-        <is>
-          <t>Brennan</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>brennanines@gmail.com</t>
-        </is>
-      </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>Brandi</t>
-        </is>
-      </c>
-      <c r="B482" t="inlineStr">
-        <is>
-          <t>Middel</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>brandimiddel@gmail.com</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>Devan</t>
-        </is>
-      </c>
-      <c r="B483" t="inlineStr">
-        <is>
-          <t>Krahn</t>
-        </is>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>de_vo_brown@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>cainsley</t>
-        </is>
-      </c>
-      <c r="B484" t="inlineStr">
-        <is>
-          <t>coleman</t>
-        </is>
-      </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>mattwhitecotton+3@shaw.ca</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>Jyzzle</t>
-        </is>
-      </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>Rosano</t>
-        </is>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>jhinengskii@gmail.com</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>Nicole</t>
-        </is>
-      </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>Hobbs</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>nicoldatalina.h@gmail.com</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>Alyssa</t>
-        </is>
-      </c>
-      <c r="B487" t="inlineStr">
-        <is>
-          <t>Bates</t>
-        </is>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>ambates@shaw.ca</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>Neal</t>
-        </is>
-      </c>
-      <c r="B488" t="inlineStr">
-        <is>
-          <t>Edillon</t>
-        </is>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>nedillon@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>Ella</t>
-        </is>
-      </c>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>Mariveles</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>ellamariveles16@gmail.com</t>
-        </is>
-      </c>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>Jeffrey</t>
-        </is>
-      </c>
-      <c r="B490" t="inlineStr">
-        <is>
-          <t>Cao</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>dr.jeffreycao@gmail.com</t>
-        </is>
-      </c>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>James</t>
-        </is>
-      </c>
-      <c r="B491" t="inlineStr">
-        <is>
-          <t>Anabieza</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>jamesanabieza@icloud.com</t>
-        </is>
-      </c>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="B492" t="inlineStr">
-        <is>
-          <t>Prete</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>mattprete1967@gmail.com</t>
-        </is>
-      </c>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>Jeip</t>
-        </is>
-      </c>
-      <c r="B493" t="inlineStr">
-        <is>
-          <t>Geneblazo</t>
-        </is>
-      </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>jigblaze@gmail.com</t>
-        </is>
-      </c>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>Mark</t>
-        </is>
-      </c>
-      <c r="B494" t="inlineStr">
-        <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>santosfamily11@icloud.com</t>
-        </is>
-      </c>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>Izzy</t>
-        </is>
-      </c>
-      <c r="B495" t="inlineStr">
-        <is>
-          <t>Prete</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>izzyprete11@gmail.com</t>
-        </is>
-      </c>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>Jose</t>
-        </is>
-      </c>
-      <c r="B496" t="inlineStr">
-        <is>
-          <t>Monzon</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>jose.monzon@hotmail.ca</t>
-        </is>
-      </c>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>Roman</t>
-        </is>
-      </c>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>Prete</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>shawnaprete+1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>Ray</t>
-        </is>
-      </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>Recto</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>rayray780@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>Mark</t>
-        </is>
-      </c>
-      <c r="B499" t="inlineStr">
-        <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="C499" t="inlineStr">
-        <is>
-          <t>markanddebra@shaw.ca</t>
-        </is>
-      </c>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>Angelbert</t>
-        </is>
-      </c>
-      <c r="B500" t="inlineStr">
-        <is>
-          <t>David</t>
-        </is>
-      </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>tenshi04@gmail.com</t>
-        </is>
-      </c>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>Shawna</t>
-        </is>
-      </c>
-      <c r="B501" t="inlineStr">
-        <is>
-          <t>Prete</t>
-        </is>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>shawnaprete@gmail.com</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>Robin</t>
-        </is>
-      </c>
-      <c r="B502" t="inlineStr">
-        <is>
-          <t>Espino</t>
-        </is>
-      </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>robinespino@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>Keith</t>
-        </is>
-      </c>
-      <c r="B503" t="inlineStr">
-        <is>
-          <t>Balante</t>
-        </is>
-      </c>
-      <c r="C503" t="inlineStr">
-        <is>
-          <t>kbalante@gmail.com</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>karin</t>
-        </is>
-      </c>
-      <c r="B504" t="inlineStr">
-        <is>
-          <t>pearce</t>
-        </is>
-      </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>karin-denise@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D504" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>Nathan</t>
-        </is>
-      </c>
-      <c r="B505" t="inlineStr">
-        <is>
-          <t>Davies</t>
-        </is>
-      </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>nathan@davies.tech</t>
-        </is>
-      </c>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>Tracy</t>
-        </is>
-      </c>
-      <c r="B506" t="inlineStr">
-        <is>
-          <t>Ray</t>
-        </is>
-      </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>tracyray@telus.net</t>
-        </is>
-      </c>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>lyla</t>
-        </is>
-      </c>
-      <c r="B507" t="inlineStr">
-        <is>
-          <t>rowe</t>
-        </is>
-      </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>lyla.rowe@shaw.ca</t>
-        </is>
-      </c>
-      <c r="D507" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>Cohen</t>
-        </is>
-      </c>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="C508" t="inlineStr"/>
-      <c r="D508" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>jerry</t>
-        </is>
-      </c>
-      <c r="B509" t="inlineStr">
-        <is>
-          <t>rowe</t>
-        </is>
-      </c>
-      <c r="C509" t="inlineStr">
-        <is>
-          <t>jnrowe72@gmail.com</t>
-        </is>
-      </c>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>Jon</t>
-        </is>
-      </c>
-      <c r="B510" t="inlineStr">
-        <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="C510" t="inlineStr">
-        <is>
-          <t>jondeanestewart@gmail.com</t>
-        </is>
-      </c>
-      <c r="D510" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>Paula Mae</t>
-        </is>
-      </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>Magpayo</t>
-        </is>
-      </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>aluapeam@gmail.com</t>
-        </is>
-      </c>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>Jason</t>
-        </is>
-      </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>Snider</t>
-        </is>
-      </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>jason@rdlawyers.ca</t>
-        </is>
-      </c>
-      <c r="D512" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>Robin</t>
-        </is>
-      </c>
-      <c r="B513" t="inlineStr">
-        <is>
-          <t>Snider</t>
-        </is>
-      </c>
-      <c r="C513" t="inlineStr">
-        <is>
-          <t>robin.snider22@gmail.com</t>
-        </is>
-      </c>
-      <c r="D513" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>Erin</t>
-        </is>
-      </c>
-      <c r="B514" t="inlineStr">
-        <is>
-          <t>Bollinger</t>
-        </is>
-      </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>teawitherinb@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D514" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>Tony</t>
-        </is>
-      </c>
-      <c r="B515" t="inlineStr">
-        <is>
-          <t>Goutbeck</t>
-        </is>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>gouter@live.ca</t>
-        </is>
-      </c>
-      <c r="D515" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>Erin</t>
-        </is>
-      </c>
-      <c r="B516" t="inlineStr">
-        <is>
-          <t>Porodanuk</t>
-        </is>
-      </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>erin.porodanuk@gmail.com</t>
-        </is>
-      </c>
-      <c r="D516" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>Marie-Astrid</t>
-        </is>
-      </c>
-      <c r="B517" t="inlineStr">
-        <is>
-          <t>Detharet</t>
-        </is>
-      </c>
-      <c r="C517" t="inlineStr">
-        <is>
-          <t>mdetharet@cesd73.ca</t>
-        </is>
-      </c>
-      <c r="D517" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>Brian</t>
-        </is>
-      </c>
-      <c r="B518" t="inlineStr">
-        <is>
-          <t>Rubia</t>
-        </is>
-      </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>brianrubia@gmail.com</t>
-        </is>
-      </c>
-      <c r="D518" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>Leanna</t>
-        </is>
-      </c>
-      <c r="B519" t="inlineStr">
-        <is>
-          <t>Barillo</t>
-        </is>
-      </c>
-      <c r="C519" t="inlineStr">
-        <is>
-          <t>leanna.barillo@gmail.com</t>
-        </is>
-      </c>
-      <c r="D519" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="B520" t="inlineStr">
-        <is>
-          <t>Mamac</t>
-        </is>
-      </c>
-      <c r="C520" t="inlineStr">
-        <is>
-          <t>paula.mamac@gmail.com</t>
-        </is>
-      </c>
-      <c r="D520" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>Victor</t>
-        </is>
-      </c>
-      <c r="B521" t="inlineStr">
-        <is>
-          <t>Tan</t>
-        </is>
-      </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>victor.tan@gmail.com</t>
-        </is>
-      </c>
-      <c r="D521" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>Sharleen</t>
-        </is>
-      </c>
-      <c r="B522" t="inlineStr">
-        <is>
-          <t>Mamac</t>
-        </is>
-      </c>
-      <c r="C522" t="inlineStr">
-        <is>
-          <t>lacacapam@gmail.com</t>
-        </is>
-      </c>
-      <c r="D522" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>Nicolas</t>
-        </is>
-      </c>
-      <c r="B523" t="inlineStr">
-        <is>
-          <t>Crooks</t>
-        </is>
-      </c>
-      <c r="C523" t="inlineStr">
-        <is>
-          <t>devin.crooks13@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D523" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>Mary Ann</t>
-        </is>
-      </c>
-      <c r="B524" t="inlineStr">
-        <is>
-          <t>Revosura</t>
-        </is>
-      </c>
-      <c r="C524" t="inlineStr">
-        <is>
-          <t>mayannrevosura@gmail.com</t>
-        </is>
-      </c>
-      <c r="D524" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>Primery</t>
-        </is>
-      </c>
-      <c r="B525" t="inlineStr">
-        <is>
-          <t>Munez</t>
-        </is>
-      </c>
-      <c r="C525" t="inlineStr">
-        <is>
-          <t>primererymunez@gmail.com</t>
-        </is>
-      </c>
-      <c r="D525" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>Annissa</t>
-        </is>
-      </c>
-      <c r="B526" t="inlineStr">
-        <is>
-          <t>Crooks</t>
-        </is>
-      </c>
-      <c r="C526" t="inlineStr">
-        <is>
-          <t>devin.crooks12@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D526" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>Jose</t>
-        </is>
-      </c>
-      <c r="B527" t="inlineStr">
-        <is>
-          <t>Pizaarres</t>
-        </is>
-      </c>
-      <c r="C527" t="inlineStr">
-        <is>
-          <t>josepizaarres@gmail.com</t>
-        </is>
-      </c>
-      <c r="D527" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>Janelle</t>
-        </is>
-      </c>
-      <c r="B528" t="inlineStr">
-        <is>
-          <t>Dionalavo</t>
-        </is>
-      </c>
-      <c r="C528" t="inlineStr">
-        <is>
-          <t>janelle@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D528" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>Franka</t>
-        </is>
-      </c>
-      <c r="B529" t="inlineStr">
-        <is>
-          <t>Two</t>
-        </is>
-      </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>franka.two@gmail.com</t>
-        </is>
-      </c>
-      <c r="D529" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>Steve</t>
-        </is>
-      </c>
-      <c r="B530" t="inlineStr">
-        <is>
-          <t>Porodnauk</t>
-        </is>
-      </c>
-      <c r="C530" t="inlineStr">
-        <is>
-          <t>steven.porodnauk@gmail.com</t>
-        </is>
-      </c>
-      <c r="D530" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>Nicole</t>
-        </is>
-      </c>
-      <c r="B531" t="inlineStr">
-        <is>
-          <t>Burkmar</t>
-        </is>
-      </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>nburkmar@gmail.com</t>
-        </is>
-      </c>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>Ma Treshia Mai</t>
-        </is>
-      </c>
-      <c r="B532" t="inlineStr">
-        <is>
-          <t>Mamac</t>
-        </is>
-      </c>
-      <c r="C532" t="inlineStr">
-        <is>
-          <t>treshia.mamac@gmail.com</t>
-        </is>
-      </c>
-      <c r="D532" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>Devin</t>
-        </is>
-      </c>
-      <c r="B533" t="inlineStr">
-        <is>
-          <t>Crooks</t>
-        </is>
-      </c>
-      <c r="C533" t="inlineStr">
-        <is>
-          <t>devincrooks@hotmail.com</t>
-        </is>
-      </c>
-      <c r="D533" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
-        <is>
-          <t>Aaron</t>
-        </is>
-      </c>
-      <c r="B534" t="inlineStr">
-        <is>
-          <t>Richter</t>
-        </is>
-      </c>
-      <c r="C534" t="inlineStr">
-        <is>
-          <t>richter_aaron@yahoo.ca</t>
-        </is>
-      </c>
-      <c r="D534" t="inlineStr">
-        <is>
-          <t>reddeer@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>Jennifer</t>
-        </is>
-      </c>
-      <c r="B535" t="inlineStr">
-        <is>
-          <t>Marvious</t>
-        </is>
-      </c>
-      <c r="C535" t="inlineStr">
-        <is>
-          <t>jennifer.marvoius@gmail.com</t>
-        </is>
-      </c>
-      <c r="D535" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Red_Deer.xlsx
+++ b/docs/downloads/Red_Deer.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D365"/>
+  <dimension ref="A1:D408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6447,15 +6447,19 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Ellie</t>
+          <t>Jeanne</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Glover</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr"/>
+          <t>Botha</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>righsbotha@gmail.com</t>
+        </is>
+      </c>
       <c r="D309" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6465,15 +6469,19 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Wendy</t>
+          <t>Deon</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Glover</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr"/>
+          <t>Botha</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>jidh300@gmail.com</t>
+        </is>
+      </c>
       <c r="D310" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6483,7 +6491,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Ellie</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -6501,19 +6509,15 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Shakil</t>
+          <t>Wendy</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Papel</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>sk17papel@gmail.com</t>
-        </is>
-      </c>
+          <t>Glover</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6523,12 +6527,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Alyssa</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Sherwin</t>
+          <t>Glover</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
@@ -6541,15 +6545,19 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Seth</t>
+          <t>Shakil</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Gill</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr"/>
+          <t>Papel</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>sk17papel@gmail.com</t>
+        </is>
+      </c>
       <c r="D314" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6559,12 +6567,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Jai-Li</t>
+          <t>Alyssa</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Harvey</t>
+          <t>Sherwin</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
@@ -6577,12 +6585,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Raine</t>
+          <t>Seth</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Joson</t>
+          <t>Gill</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
@@ -6595,12 +6603,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Isaac</t>
+          <t>Jai-Li</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Park</t>
+          <t>Harvey</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
@@ -6613,12 +6621,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Fisher</t>
+          <t>Raine</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Dunphy</t>
+          <t>Joson</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
@@ -6631,12 +6639,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Ayden</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Quinlan</t>
+          <t>Park</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
@@ -6649,12 +6657,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>Fisher</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>Dunphy</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
@@ -6667,12 +6675,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Marah</t>
+          <t>Ayden</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Dunphy</t>
+          <t>Quinlan</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
@@ -6685,12 +6693,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Fleck</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
@@ -6703,12 +6711,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Marah</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>McRae</t>
+          <t>Dunphy</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
@@ -6721,19 +6729,15 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Hanna</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Safron</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>hannasafron@icloud.com</t>
-        </is>
-      </c>
+          <t>Fleck</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6743,12 +6747,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Howard</t>
+          <t>McRae</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
@@ -6761,17 +6765,17 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Mila</t>
+          <t>Hanna</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Haynes</t>
+          <t>Safron</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>cristinabagundol@yahoo.com</t>
+          <t>hannasafron@icloud.com</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -6783,12 +6787,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Robberstad</t>
+          <t>Howard</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
@@ -6801,15 +6805,19 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Shayne</t>
+          <t>Mila</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Malsbury</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr"/>
+          <t>Haynes</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>cristinabagundol@yahoo.com</t>
+        </is>
+      </c>
       <c r="D328" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6819,19 +6827,15 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>laura</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>edwards</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>alfedwards58@gmail.com</t>
-        </is>
-      </c>
+          <t>Robberstad</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6841,12 +6845,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Shayne</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>McClelland</t>
+          <t>Malsbury</t>
         </is>
       </c>
       <c r="C330" t="inlineStr"/>
@@ -6859,15 +6863,19 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Larry</t>
+          <t>laura</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Vetter</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr"/>
+          <t>edwards</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>alfedwards58@gmail.com</t>
+        </is>
+      </c>
       <c r="D331" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6877,12 +6885,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Vetter</t>
+          <t>McClelland</t>
         </is>
       </c>
       <c r="C332" t="inlineStr"/>
@@ -6895,12 +6903,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Larry</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Fuchs</t>
+          <t>Vetter</t>
         </is>
       </c>
       <c r="C333" t="inlineStr"/>
@@ -6913,12 +6921,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Meyer</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Fuchs</t>
+          <t>Vetter</t>
         </is>
       </c>
       <c r="C334" t="inlineStr"/>
@@ -6931,19 +6939,15 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Serenna</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Constable</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>reddeer@bredin.ca</t>
-        </is>
-      </c>
+          <t>Fuchs</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6953,19 +6957,15 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Carter</t>
+          <t>Meyer</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Proft</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>carter.proft@iaprivatewealth.ca</t>
-        </is>
-      </c>
+          <t>Fuchs</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6975,17 +6975,17 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Sakthi</t>
+          <t>Serenna</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Aenugula</t>
+          <t>Constable</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>sakthiprasanth.aenugula@novachem.com</t>
+          <t>reddeer@bredin.ca</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -6997,15 +6997,19 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Nikki</t>
+          <t>Carter</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Januszewski</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr"/>
+          <t>Proft</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>carter.proft@iaprivatewealth.ca</t>
+        </is>
+      </c>
       <c r="D338" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7015,15 +7019,19 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Buffy</t>
+          <t>Sakthi</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Robblee</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr"/>
+          <t>Aenugula</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>sakthiprasanth.aenugula@novachem.com</t>
+        </is>
+      </c>
       <c r="D339" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7033,7 +7041,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Zoey</t>
+          <t>Nikki</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -7051,12 +7059,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Buffy</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>McPeek</t>
+          <t>Robblee</t>
         </is>
       </c>
       <c r="C341" t="inlineStr"/>
@@ -7069,7 +7077,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Ella</t>
+          <t>Zoey</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -7087,12 +7095,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Barb</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Pfannmueler</t>
+          <t>McPeek</t>
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
@@ -7105,12 +7113,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Adyson</t>
+          <t>Ella</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Trepanier</t>
+          <t>Januszewski</t>
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
@@ -7123,12 +7131,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Barb</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Trepanier</t>
+          <t>Pfannmueler</t>
         </is>
       </c>
       <c r="C345" t="inlineStr"/>
@@ -7141,7 +7149,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Adyson</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -7159,19 +7167,15 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Megan &amp; John</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Heinen</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>maheinen84@gmail.com</t>
-        </is>
-      </c>
+          <t>Trepanier</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7181,12 +7185,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Cote</t>
+          <t>Trepanier</t>
         </is>
       </c>
       <c r="C348" t="inlineStr"/>
@@ -7199,15 +7203,19 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Jayda</t>
+          <t>Megan &amp; John</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Differenz</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr"/>
+          <t>Heinen</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>maheinen84@gmail.com</t>
+        </is>
+      </c>
       <c r="D349" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7217,19 +7225,15 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>julien</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>kelly</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>kellyseamus=+1@hotmail.com</t>
-        </is>
-      </c>
+          <t>Cote</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7239,19 +7243,15 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Jayda</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Davison</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>jldav78@gmail.com</t>
-        </is>
-      </c>
+          <t>Differenz</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7261,17 +7261,17 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Kaitlin</t>
+          <t>julien</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Meier</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>kmeier@pivotalcpa.ca</t>
+          <t>kellyseamus=+1@hotmail.com</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -7283,17 +7283,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Tristin</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Brisbois</t>
+          <t>Davison</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>tristin.brisbois@reddeer.ca</t>
+          <t>jldav78@gmail.com</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -7305,17 +7305,17 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>leslie</t>
+          <t>Kaitlin</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>wright</t>
+          <t>Meier</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>leslie0985@hotmail.com</t>
+          <t>kmeier@pivotalcpa.ca</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -7327,15 +7327,19 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Tristin</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr"/>
+          <t>Brisbois</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>tristin.brisbois@reddeer.ca</t>
+        </is>
+      </c>
       <c r="D355" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7345,15 +7349,19 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Seija</t>
+          <t>leslie</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Worth</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr"/>
+          <t>wright</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>leslie0985@hotmail.com</t>
+        </is>
+      </c>
       <c r="D356" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7363,12 +7371,12 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Elias</t>
+          <t>Hunter</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Worth</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="C357" t="inlineStr"/>
@@ -7381,19 +7389,15 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Khryzzia Kaye</t>
+          <t>Seija</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Mendio</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>mendio.kaye@gmail.com</t>
-        </is>
-      </c>
+          <t>Worth</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr"/>
       <c r="D358" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7403,12 +7407,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Cohen</t>
+          <t>Elias</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Stewart</t>
+          <t>Worth</t>
         </is>
       </c>
       <c r="C359" t="inlineStr"/>
@@ -7421,17 +7425,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Khryzzia Kaye</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Snider</t>
+          <t>Mendio</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>jason@rdlawyers.ca</t>
+          <t>mendio.kaye@gmail.com</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -7443,12 +7447,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Quinn</t>
+          <t>Cohen</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Schmaltz</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="C361" t="inlineStr"/>
@@ -7461,15 +7465,19 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Kilbreath</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr"/>
+          <t>Snider</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>jason@rdlawyers.ca</t>
+        </is>
+      </c>
       <c r="D362" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7479,12 +7487,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Jovi</t>
+          <t>Quinn</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Kilbreath</t>
+          <t>Schmaltz</t>
         </is>
       </c>
       <c r="C363" t="inlineStr"/>
@@ -7497,7 +7505,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -7515,7 +7523,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Rio</t>
+          <t>Jovi</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -7525,6 +7533,940 @@
       </c>
       <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Kilbreath</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Rio</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Kilbreath</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Christal</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Coupland</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>christalmargaret@gmail.com</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Candace</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Misyk</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>cmisyk@gmail.com</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>jack</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>misyk</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>cmisyk+1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Brenda</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Tams</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>tamsbrenda@gamil.com</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Rick</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Tams</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>tamsfarm@xplornet.ca</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Rommel</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Buriel</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>romjoy.rainbow@gmail.com</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Calvin</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Maranga</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>calvinmaranga16@gmail.com</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Spicer</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>albrea1971@gmail.com</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Denise</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Maranga</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>denden.mushii@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Heather</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Griffiths</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>heather_mclaren@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Judy</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Toor</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>judy.toor@gmail.com</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>clarissa</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>maranga</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>clarissa_maranga@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Doug</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Maranga</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>doug.maranga@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Harper</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Griffiths</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Samuel</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Ho</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>sammy.shogun@gmail.com</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Jerry</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Espino</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>jerryespino@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Rodney</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Lim</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>rodneylim46@gmail.com</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Aggarwal</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>westparkida@gmail.com</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>greg</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>pollan</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>gregpollon65@outlook.com</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Kenneth</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Tong</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>tongk88@gmail.com</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Marianne</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Badenhorst</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>mariannebadenhorst@gmail.com</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Dale</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Joyal</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>daleajoyal1963@gmasil.com</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Terry</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Tonsi</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>ttonsi@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Gail</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Sanders</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>sesrungail@gmail.com</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Sheila</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Crouch</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>sheila+@pickleplex.ca</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Sanders</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>rgswildcat1@outlook.com</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Candace</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Tonsi</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>ctonsi@hotmail.ca</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Darling</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>jd@mapletree.ca</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Andreas</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Kusuma</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>macogpk@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Volunteer</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>RDPC</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>club+@reddeerpickleball.com</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Wade</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Schafer</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>wschafer08@gmail.com</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Bell</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>jonnnybell@gmail.com</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Carly</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Farion</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>carlyfarion@telus.net</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>RDPC</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Tournament</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>treasurer@reddeerpickleball.com</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Erin</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>esmith01@live.ca</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Samantha</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Carruthers</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>sammulake@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Hollett</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>gdhollet@icloud.com</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Presley</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>sarahpresley36@gmail.com</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Judy</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Toor</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>m-poor@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Elina</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Upward</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>elinabelle2014@gmail.com</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Carter</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>jessica.e.arterone@gmail.com</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Red_Deer.xlsx
+++ b/docs/downloads/Red_Deer.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D408"/>
+  <dimension ref="A1:D426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8472,6 +8472,398 @@
         </is>
       </c>
     </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Ken</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Elver</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>ken.alver@gmail.com</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Samantha</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Schellenberg</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>hischellenberg@gmail.com</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Reid</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Prystai</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>reid.prystai@gmail.com</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Matt</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Walsh</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>matt.walsh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>PATTERSON</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>rjpatterson101@googlemail.com</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Hreat</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Bnabsa</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>hreatbba24@gmail.com</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Suzanne</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Aylward</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>suzanneaylward@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Henry</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Schellenberg</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Armstrong</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>carriearmstrong+1@live.com</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Keith</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Spady</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>spadybk@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Charolette</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Doffett</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>charolette.doffett@gmail.com</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Walters</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>nancyjoy@telus.net</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Chandler</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Duffett</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>chandler.duffett@gmail.com</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Amanda</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Wilson</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>amanda.wilson@rdpsd.ab.ca</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Patrica</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Viado</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>patricaviado@gmail.com</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Prystai</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>michelle.yunnch@gmail.com</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Horembala</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>paddling@telus.net</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Carrie</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Armstrong</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>carriearmstrong@live.com</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/downloads/Red_Deer.xlsx
+++ b/docs/downloads/Red_Deer.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D426"/>
+  <dimension ref="A1:D467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1293,17 +1293,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Cathy</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wyntjes</t>
+          <t>Odenbach</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>dylanwynjes@hotmail.com</t>
+          <t>codenbach@gmail.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1315,17 +1315,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Wyntjes</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>wilsonjp76@gmail.com</t>
+          <t>dylanwynjes@hotmail.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1337,17 +1337,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Townsend</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>julie@townsendelectrical.ca</t>
+          <t>wilsonjp76@gmail.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1359,17 +1359,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tommy jr 2</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Paquette</t>
+          <t>Townsend</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>anthony.paq269+2@gmail.com</t>
+          <t>julie@townsendelectrical.ca</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1381,17 +1381,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Laurie</t>
+          <t>Tommy jr 2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hubley</t>
+          <t>Paquette</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>hubley+1@awink.com</t>
+          <t>anthony.paq269+2@gmail.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1403,17 +1403,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jake</t>
+          <t>Laurie</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Brooks</t>
+          <t>Hubley</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jakenb737@gmail.com</t>
+          <t>hubley+1@awink.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1425,17 +1425,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Patricia</t>
+          <t>Jake</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lim</t>
+          <t>Brooks</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>patricialim19@gmail.com</t>
+          <t>jakenb737@gmail.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1447,17 +1447,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Patricia</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Blair</t>
+          <t>Lim</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>dmboard@telus.net</t>
+          <t>patricialim19@gmail.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1469,17 +1469,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Malika</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Yohan</t>
+          <t>Blair</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>yohansilba205@gmail.com</t>
+          <t>dmboard@telus.net</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1491,17 +1491,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Malika</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pochylko</t>
+          <t>Yohan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>lucas@andystrucksales.com</t>
+          <t>yohansilba205@gmail.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1513,17 +1513,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Parry</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dyck</t>
+          <t>Pochylko</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>donutm@telus.net</t>
+          <t>lucas@andystrucksales.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1535,17 +1535,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Parry</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lim</t>
+          <t>Dyck</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>bentholim@gmail.com</t>
+          <t>donutm@telus.net</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1557,17 +1557,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Townsend</t>
+          <t>Lim</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>scott@townsendelectrical.ca</t>
+          <t>bentholim@gmail.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1579,17 +1579,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lecompte</t>
+          <t>Townsend</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>michellelecompte1@gmail.com</t>
+          <t>scott@townsendelectrical.ca</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1601,17 +1601,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Derrek</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Halberson</t>
+          <t>Lecompte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>derrekhalberson@gmail.com</t>
+          <t>michellelecompte1@gmail.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1623,17 +1623,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Nikki</t>
+          <t>Derrek</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Lastname</t>
+          <t>Halberson</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>chia-fray-1g@icloud.com</t>
+          <t>derrekhalberson@gmail.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1645,17 +1645,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Red deer</t>
+          <t>Nikki</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Lastname</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>reddeeraccounting@pickleplexclub.ca</t>
+          <t>chia-fray-1g@icloud.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1667,17 +1667,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Red deer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Monville</t>
+          <t>Accounting</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>thomas@monvillelandscaping.com</t>
+          <t>reddeeraccounting@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1689,17 +1689,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Swenson</t>
+          <t>Monville</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>gregswenson04@gmail.com</t>
+          <t>thomas@monvillelandscaping.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1711,17 +1711,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Kingsley</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Grice</t>
+          <t>Swenson</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>grice_kingsley@hotmail.com</t>
+          <t>gregswenson04@gmail.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1733,17 +1733,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Shayne</t>
+          <t>Kingsley</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Luchsinger</t>
+          <t>Grice</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>hdhobo@gmail.com</t>
+          <t>grice_kingsley@hotmail.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1755,17 +1755,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Antonthy</t>
+          <t>Shayne</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Judd</t>
+          <t>Luchsinger</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>anthony.judd@ig.ca</t>
+          <t>hdhobo@gmail.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1777,17 +1777,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Rick</t>
+          <t>Antonthy</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Adie</t>
+          <t>Judd</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>hugo2196@proton.me</t>
+          <t>anthony.judd@ig.ca</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1799,17 +1799,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Kris</t>
+          <t>Rick</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Krzysik</t>
+          <t>Adie</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>kriskrzysik@hotmail.com</t>
+          <t>hugo2196@proton.me</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1821,17 +1821,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Elena</t>
+          <t>Kris</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Durette</t>
+          <t>Krzysik</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ejdurett+1@gmail.com</t>
+          <t>kriskrzysik@hotmail.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1843,17 +1843,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Branden</t>
+          <t>Elena</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Macdonald</t>
+          <t>Durette</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>brandenmac@gmail.com</t>
+          <t>ejdurett+1@gmail.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1865,17 +1865,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Branden</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Peden</t>
+          <t>Macdonald</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>julieapeden@gmail.com</t>
+          <t>brandenmac@gmail.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1887,17 +1887,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Macpherson</t>
+          <t>Peden</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ethanmac@yahoo.ca</t>
+          <t>julieapeden@gmail.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1909,17 +1909,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Steven</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Thomlison</t>
+          <t>Macpherson</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>schrest+2@telusplanet.net</t>
+          <t>ethanmac@yahoo.ca</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1931,17 +1931,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Yannick</t>
+          <t>Steven</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Reid</t>
+          <t>Thomlison</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>reidroamer@gmail.com</t>
+          <t>schrest+2@telusplanet.net</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ava</t>
+          <t>Yannick</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bilo</t>
+          <t>Reid</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>avabee314@gmail.com</t>
+          <t>reidroamer@gmail.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1975,17 +1975,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Axton</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Grutterink</t>
+          <t>Bilo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>hjgrutterink+7@hotmail.com</t>
+          <t>avabee314@gmail.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1997,17 +1997,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Debbie</t>
+          <t>Axton</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Salmon</t>
+          <t>Grutterink</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>debesalmon@gmail.com</t>
+          <t>hjgrutterink+7@hotmail.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2019,17 +2019,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Darcy</t>
+          <t>Debbie</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Marquart</t>
+          <t>Salmon</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>darcymarquart@gmail.com</t>
+          <t>debesalmon@gmail.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2041,17 +2041,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Seth</t>
+          <t>Darcy</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Gill</t>
+          <t>Marquart</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>sethg0202@gmail.com</t>
+          <t>darcymarquart@gmail.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2063,17 +2063,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Benno</t>
+          <t>Seth</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fath</t>
+          <t>Gill</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>butse.ls@gmail.com</t>
+          <t>sethg0202@gmail.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2085,17 +2085,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Chay</t>
+          <t>Benno</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Feuser</t>
+          <t>Fath</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>chay_feuser@hotmail.com</t>
+          <t>butse.ls@gmail.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2107,17 +2107,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Dwayne</t>
+          <t>Chay</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mcarthur</t>
+          <t>Feuser</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>sands1@telusplanet.net</t>
+          <t>chay_feuser@hotmail.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2129,17 +2129,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Dwayne</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Genereux</t>
+          <t>Mcarthur</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>emgrose@telus.net</t>
+          <t>sands1@telusplanet.net</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2151,17 +2151,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Tony</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Judd</t>
+          <t>Genereux</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>a_judd@live.com</t>
+          <t>emgrose@telus.net</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2173,17 +2173,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Tony</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Delaronde</t>
+          <t>Judd</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>melissa_delaronde@hotmail.com</t>
+          <t>a_judd@live.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2195,17 +2195,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Annie</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Collins</t>
+          <t>Delaronde</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>annie.collins0319@gmail.com</t>
+          <t>melissa_delaronde@hotmail.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2217,17 +2217,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Annie</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Langard</t>
+          <t>Collins</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>jordanlangard@gmail.com</t>
+          <t>annie.collins0319@gmail.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2239,17 +2239,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Yapa</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Banbara</t>
+          <t>Langard</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>yapa1@mail.com</t>
+          <t>jordanlangard@gmail.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2261,17 +2261,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Holly</t>
+          <t>Yapa</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Mundorf</t>
+          <t>Banbara</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>theartturtle@gmail.com</t>
+          <t>yapa1@mail.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2283,17 +2283,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Helen</t>
+          <t>Holly</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Swanson</t>
+          <t>Mundorf</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>watercoursewaystudio@gmail.com</t>
+          <t>theartturtle@gmail.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2305,17 +2305,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Dom</t>
+          <t>Helen</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Gomes</t>
+          <t>Swanson</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>domgomesmedia@gmail.com</t>
+          <t>watercoursewaystudio@gmail.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2327,17 +2327,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sau mei</t>
+          <t>Dom</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>Gomes</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>lamsaumei510@gmail.com</t>
+          <t>domgomesmedia@gmail.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2349,15 +2349,19 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Sau mei</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Pylypets</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>Lam</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>lamsaumei510@gmail.com</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -2367,19 +2371,15 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Frank</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Gallie</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>frank1gallie1@gmail.com</t>
-        </is>
-      </c>
+          <t>Pylypets</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -2389,15 +2389,19 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Nahum</t>
+          <t>Frank</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Pinette</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>Gallie</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>frank1gallie1@gmail.com</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -2407,19 +2411,15 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Brenda</t>
+          <t>Nahum</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Bale</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>bcalvin4@gmail.com</t>
-        </is>
-      </c>
+          <t>Pinette</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -2429,15 +2429,19 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Carl Michael</t>
+          <t>Brenda</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Meneses</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>Bale</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>bcalvin4@gmail.com</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -2447,12 +2451,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Carl Michael</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Lenton</t>
+          <t>Meneses</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -2465,12 +2469,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Armstrong</t>
+          <t>Lenton</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -2483,12 +2487,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sydney</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Pillman</t>
+          <t>Armstrong</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2501,12 +2505,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Sydney</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Watt</t>
+          <t>Pillman</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2519,19 +2523,15 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Maddie</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Bladds</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>md.blades17@gmail.com</t>
-        </is>
-      </c>
+          <t>Watt</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -2541,15 +2541,19 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Reese</t>
+          <t>Maddie</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Meikle</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
+          <t>Bladds</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>md.blades17@gmail.com</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -2559,12 +2563,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Reese</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Labrecque</t>
+          <t>Meikle</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -2577,19 +2581,15 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>andrew</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>feuser</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>andrew.feuser@gmail.com</t>
-        </is>
-      </c>
+          <t>Labrecque</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -2599,15 +2599,19 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Adriana</t>
+          <t>andrew</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>VanLochem</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
+          <t>feuser</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>andrew.feuser@gmail.com</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -2617,12 +2621,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>Adriana</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Blum</t>
+          <t>VanLochem</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -2635,12 +2639,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Criszel</t>
+          <t>Aiden</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Maraon</t>
+          <t>Blum</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -2653,12 +2657,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Hailey</t>
+          <t>Criszel</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>Maraon</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -2671,12 +2675,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Brooks</t>
+          <t>Hailey</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Hansen</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -2689,12 +2693,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Paxton</t>
+          <t>Brooks</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Hansen</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -2707,12 +2711,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Taya</t>
+          <t>Paxton</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ferguson</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2725,12 +2729,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Taya</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Glimsdale</t>
+          <t>Ferguson</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2743,12 +2747,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Olson</t>
+          <t>Glimsdale</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2761,12 +2765,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Bowen</t>
+          <t>Aiden</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Olson</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2779,12 +2783,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AJ</t>
+          <t>Bowen</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Celis</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2797,12 +2801,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Steven</t>
+          <t>AJ</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ruppert</t>
+          <t>Celis</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2815,12 +2819,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Steven</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Bousquet</t>
+          <t>Ruppert</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2833,12 +2837,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Devin</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Holzer</t>
+          <t>Bousquet</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2851,12 +2855,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>Holzer</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2869,12 +2873,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2887,12 +2891,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>VanLochem</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2905,12 +2909,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Liebig</t>
+          <t>VanLochem</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2923,12 +2927,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Tessa</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>Liebig</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2941,12 +2945,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Tessa</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Bakker</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2959,12 +2963,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Bakker</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2977,12 +2981,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Judd</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2995,12 +2999,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Bovey</t>
+          <t>Judd</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -3013,12 +3017,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Michnik</t>
+          <t>Bovey</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -3031,12 +3035,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Blum</t>
+          <t>Michnik</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -3049,12 +3053,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Jaykob</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Oickle</t>
+          <t>Blum</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -3067,12 +3071,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Jaykob</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ayuno</t>
+          <t>Oickle</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -3085,12 +3089,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Gage</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Liebig</t>
+          <t>Ayuno</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -3103,12 +3107,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Tenley</t>
+          <t>Gage</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>Liebig</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -3121,12 +3125,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Karston</t>
+          <t>Tenley</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Loehndorf</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -3139,12 +3143,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Bbbb</t>
+          <t>Karston</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Dorbyk</t>
+          <t>Loehndorf</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -3157,12 +3161,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Vienne</t>
+          <t>Bbbb</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Wilkening</t>
+          <t>Dorbyk</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -3175,12 +3179,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Vienne</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Michnik</t>
+          <t>Wilkening</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -3193,12 +3197,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>VanLochem</t>
+          <t>Michnik</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -3211,12 +3215,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Alyvia</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>VanLochem</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -3229,12 +3233,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Trevor</t>
+          <t>Alyvia</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Vickery</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -3247,12 +3251,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Katelin</t>
+          <t>Trevor</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Friesen</t>
+          <t>Vickery</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -3265,12 +3269,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>Katelin</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Debogorski</t>
+          <t>Friesen</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -3283,12 +3287,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Kolton</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Balaneski</t>
+          <t>Debogorski</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -3301,12 +3305,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Crystal</t>
+          <t>Kolton</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Webber</t>
+          <t>Balaneski</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -3319,12 +3323,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MacKenzie</t>
+          <t>Crystal</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Webber</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -3337,12 +3341,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Liliam</t>
+          <t>MacKenzie</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Marinero</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -3355,12 +3359,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Franko</t>
+          <t>Liliam</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Marinero</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -3373,12 +3377,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Richelle</t>
+          <t>Franko</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Hansen</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -3391,12 +3395,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Ivy</t>
+          <t>Richelle</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Bovey</t>
+          <t>Hansen</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -3409,12 +3413,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Coen</t>
+          <t>Ivy</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Hansen</t>
+          <t>Bovey</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -3427,12 +3431,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Madison</t>
+          <t>Coen</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Judd</t>
+          <t>Hansen</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -3445,12 +3449,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Seth</t>
+          <t>Madison</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Gill</t>
+          <t>Judd</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -3463,12 +3467,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Adilynn</t>
+          <t>Seth</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Whiles</t>
+          <t>Gill</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -3481,12 +3485,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Adilynn</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Whiles</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -3499,12 +3503,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Braiden</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Michnik</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -3517,12 +3521,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Burke</t>
+          <t>Braiden</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Michnik</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -3535,12 +3539,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Jax</t>
+          <t>Burke</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -3553,12 +3557,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Jax</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Dore</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -3571,12 +3575,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Vickery</t>
+          <t>Dore</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -3589,12 +3593,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Josiah</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Oickle</t>
+          <t>Vickery</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -3607,12 +3611,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>Josiah</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Webber</t>
+          <t>Oickle</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -3625,12 +3629,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Dion</t>
+          <t>Connor</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Krause</t>
+          <t>Webber</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -3643,12 +3647,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Sophia</t>
+          <t>Dion</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Judd</t>
+          <t>Krause</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -3661,12 +3665,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Kenzy</t>
+          <t>Sophia</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Koyina</t>
+          <t>Judd</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -3679,12 +3683,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Jill</t>
+          <t>Kenzy</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Hamilton</t>
+          <t>Koyina</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -3697,12 +3701,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Stetson</t>
+          <t>Jill</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Dyck</t>
+          <t>Hamilton</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -3715,12 +3719,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Craig</t>
+          <t>Stetson</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Hamilton</t>
+          <t>Dyck</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -3733,12 +3737,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Colton</t>
+          <t>Craig</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Dyck</t>
+          <t>Hamilton</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -3751,12 +3755,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Madyson</t>
+          <t>Colton</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Koyina</t>
+          <t>Dyck</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -3769,12 +3773,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Harrison</t>
+          <t>Madyson</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Simmons</t>
+          <t>Koyina</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -3787,12 +3791,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Harrison</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Froese</t>
+          <t>Simmons</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -3805,12 +3809,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Corbin</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Dyck</t>
+          <t>Froese</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -3823,19 +3827,15 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Gunnar</t>
+          <t>Corbin</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Kilian</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>gkilian@me.com</t>
-        </is>
-      </c>
+          <t>Dyck</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -3845,15 +3845,19 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Maiya</t>
+          <t>Gunnar</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Koyina</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr"/>
+          <t>Kilian</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>gkilian@me.com</t>
+        </is>
+      </c>
       <c r="D170" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -3863,12 +3867,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Collin</t>
+          <t>Maiya</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Watts</t>
+          <t>Koyina</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -3881,19 +3885,15 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Collin</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Nicoll</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>masonrnicoll@gmail.com</t>
-        </is>
-      </c>
+          <t>Watts</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -3903,15 +3903,19 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Jin Yu</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Liang</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr"/>
+          <t>Nicoll</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>masonrnicoll@gmail.com</t>
+        </is>
+      </c>
       <c r="D173" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -3921,19 +3925,15 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Tracy</t>
+          <t>Jin Yu</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>McClelland</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>tracym1@telus.net</t>
-        </is>
-      </c>
+          <t>Liang</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -3943,17 +3943,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Abe</t>
+          <t>Tracy</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Halverson</t>
+          <t>McClelland</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>colleen.abe+1@gmail.com</t>
+          <t>tracym1@telus.net</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -3965,17 +3965,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Dianne</t>
+          <t>Abe</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Gomes</t>
+          <t>Halverson</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>dianne.gomes1@gmail.com</t>
+          <t>colleen.abe+1@gmail.com</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -3987,17 +3987,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Jody</t>
+          <t>Dianne</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Muth</t>
+          <t>Gomes</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>gramadoes@gmail.com</t>
+          <t>dianne.gomes1@gmail.com</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4009,17 +4009,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Eoin</t>
+          <t>Jody</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Wolfe</t>
+          <t>Muth</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>wolfeeion@gmail.com</t>
+          <t>gramadoes@gmail.com</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4031,15 +4031,19 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Clõy</t>
+          <t>Eoin</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Jones</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr"/>
+          <t>Wolfe</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>wolfeeion@gmail.com</t>
+        </is>
+      </c>
       <c r="D179" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4049,12 +4053,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Brielle</t>
+          <t>Clõy</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Tweten</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -4067,12 +4071,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Bennett</t>
+          <t>Brielle</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Tweten</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -4085,12 +4089,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Teagan</t>
+          <t>Bennett</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Coulter</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -4103,7 +4107,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Kinley</t>
+          <t>Teagan</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4121,12 +4125,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>McKinley</t>
+          <t>Kinley</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Coulter</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -4139,12 +4143,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Maris</t>
+          <t>McKinley</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Epp</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -4157,12 +4161,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Maris</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Polachek</t>
+          <t>Epp</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -4175,12 +4179,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Tweten</t>
+          <t>Polachek</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -4193,19 +4197,15 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Hunter</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Krywik</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>cad.support.contractors@gmail.com</t>
-        </is>
-      </c>
+          <t>Tweten</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4215,15 +4215,19 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Kayla</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Lane</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr"/>
+          <t>Krywik</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>cad.support.contractors@gmail.com</t>
+        </is>
+      </c>
       <c r="D189" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4233,12 +4237,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Joel</t>
+          <t>Kayla</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Peterman</t>
+          <t>Lane</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -4251,12 +4255,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Chase</t>
+          <t>Joel</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Girletz</t>
+          <t>Peterman</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -4269,7 +4273,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Stratten</t>
+          <t>Chase</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4287,12 +4291,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Gavin</t>
+          <t>Stratten</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t>Girletz</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -4305,12 +4309,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Gavin</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Kosola</t>
+          <t>Love</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -4323,12 +4327,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Danté</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Kosola</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -4341,12 +4345,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Brent</t>
+          <t>Danté</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -4359,12 +4363,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Rowyn</t>
+          <t>Brent</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Girletz</t>
+          <t>Young</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -4377,12 +4381,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Sheldon</t>
+          <t>Rowyn</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Girletz</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -4395,12 +4399,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Mackenzie</t>
+          <t>Sheldon</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Differenz</t>
+          <t>Lane</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -4413,12 +4417,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Quinn</t>
+          <t>Mackenzie</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Differenz</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -4431,12 +4435,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Vera</t>
+          <t>Quinn</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Kosola</t>
+          <t>Lane</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -4449,19 +4453,15 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Clint</t>
+          <t>Vera</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Buswell</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>clintbuswell@gmail.com</t>
-        </is>
-      </c>
+          <t>Kosola</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4471,7 +4471,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Rebeca</t>
+          <t>Clint</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>rebecabuswell@gmail.com</t>
+          <t>clintbuswell@gmail.com</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -4493,17 +4493,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Rebeca</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Brownell</t>
+          <t>Buswell</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>emersonbrownell@gmail.com</t>
+          <t>rebecabuswell@gmail.com</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -4515,17 +4515,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Carla</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Mccrae</t>
+          <t>Brownell</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>carlanmccrae@gmail.com</t>
+          <t>emersonbrownell@gmail.com</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -4537,17 +4537,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Carla</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Wiebe</t>
+          <t>Mccrae</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>rileywiebe@gmail.com</t>
+          <t>carlanmccrae@gmail.com</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -4559,17 +4559,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Brownell</t>
+          <t>Wiebe</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>brownel+@telus.net</t>
+          <t>rileywiebe@gmail.com</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -4581,17 +4581,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Colleen</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Githu</t>
+          <t>Brownell</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>colleengithu@gmail.com</t>
+          <t>brownel+@telus.net</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -4603,17 +4603,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Colleen</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Treu</t>
+          <t>Githu</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>ltreu@telus.net</t>
+          <t>colleengithu@gmail.com</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -4625,15 +4625,19 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Kang</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr"/>
+          <t>Treu</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>ltreu@telus.net</t>
+        </is>
+      </c>
       <c r="D210" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4643,12 +4647,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Beau</t>
+          <t>Kang</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Becker</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -4661,19 +4665,15 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Kang</t>
+          <t>Beau</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Huang</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>andrehuang74@gmail.com</t>
-        </is>
-      </c>
+          <t>Becker</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4683,15 +4683,19 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Li Juan</t>
+          <t>Kang</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Tong</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr"/>
+          <t>Huang</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>andrehuang74@gmail.com</t>
+        </is>
+      </c>
       <c r="D213" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4701,19 +4705,15 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>artur</t>
+          <t>Li Juan</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Hayrepetyan</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>hayreptyan1115@gmail.com</t>
-        </is>
-      </c>
+          <t>Tong</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4723,15 +4723,19 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>artur</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Sopkow</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr"/>
+          <t>Hayrepetyan</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>hayreptyan1115@gmail.com</t>
+        </is>
+      </c>
       <c r="D215" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -4741,12 +4745,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Emersyn</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Spina</t>
+          <t>Sopkow</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -4759,12 +4763,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Ruth</t>
+          <t>Emersyn</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Howley</t>
+          <t>Spina</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -4777,12 +4781,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Camryn</t>
+          <t>Ruth</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Spina</t>
+          <t>Howley</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -4795,12 +4799,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Piper</t>
+          <t>Camryn</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Watt</t>
+          <t>Spina</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -4813,12 +4817,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Piper</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Schurek</t>
+          <t>Watt</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -4831,12 +4835,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Adelyn</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Visser</t>
+          <t>Schurek</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -4849,12 +4853,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Harper</t>
+          <t>Adelyn</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Harnett</t>
+          <t>Visser</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -4867,12 +4871,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Blake</t>
+          <t>Harper</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Watt</t>
+          <t>Harnett</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -4885,12 +4889,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Renn</t>
+          <t>Blake</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Schurek</t>
+          <t>Watt</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -4903,12 +4907,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Lauren</t>
+          <t>Renn</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Sopkow</t>
+          <t>Schurek</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -4921,12 +4925,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Brynn</t>
+          <t>Lauren</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Watt</t>
+          <t>Sopkow</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -4939,12 +4943,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Jayde</t>
+          <t>Brynn</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Schurek</t>
+          <t>Watt</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -4957,12 +4961,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Kate</t>
+          <t>Jayde</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Sopkow</t>
+          <t>Schurek</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -4975,12 +4979,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Makenna</t>
+          <t>Kate</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Sopkow</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -4993,12 +4997,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Lainey</t>
+          <t>Makenna</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Klassen</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -5011,7 +5015,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Lainey</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5029,12 +5033,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Bryn</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Klassen</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -5047,12 +5051,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Bryn</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Klassen</t>
+          <t>Hunter</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -5065,19 +5069,15 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Bailey</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>kirstenwestberg+111@gmail.com</t>
-        </is>
-      </c>
+          <t>Klassen</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -5087,15 +5087,19 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Abbiegale</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Ryan</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr"/>
+          <t>Bailey</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>kirstenwestberg+111@gmail.com</t>
+        </is>
+      </c>
       <c r="D235" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -5105,19 +5109,15 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Talon</t>
+          <t>Abbiegale</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>O'Brien</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>talonobrien09@outlook.com</t>
-        </is>
-      </c>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -5127,7 +5127,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Sandi</t>
+          <t>Talon</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>sandals_84@hotmail.com</t>
+          <t>talonobrien09@outlook.com</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -5149,15 +5149,19 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Bbbb</t>
+          <t>Sandi</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Dorbyk</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr"/>
+          <t>O'Brien</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>sandals_84@hotmail.com</t>
+        </is>
+      </c>
       <c r="D238" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -5167,12 +5171,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Paxton</t>
+          <t>Bbbb</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Dorbyk</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -5185,12 +5189,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Madison</t>
+          <t>Paxton</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Judd</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -5203,12 +5207,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>Madison</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Debogorski</t>
+          <t>Judd</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -5221,12 +5225,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Tenley</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>Debogorski</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -5239,12 +5243,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>Tenley</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Blum</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -5262,7 +5266,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Olson</t>
+          <t>Blum</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -5275,12 +5279,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Crystal</t>
+          <t>Aiden</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Webber</t>
+          <t>Olson</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -5293,12 +5297,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Alyvia</t>
+          <t>Crystal</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>Webber</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -5311,12 +5315,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Adriana</t>
+          <t>Alyvia</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>VanLochem</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -5329,12 +5333,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Trevor</t>
+          <t>Adriana</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Vickery</t>
+          <t>VanLochem</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -5347,12 +5351,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Hailey</t>
+          <t>Trevor</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>Vickery</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -5365,12 +5369,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Anne</t>
+          <t>Hailey</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Ayuno</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -5383,12 +5387,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Jax</t>
+          <t>Anne</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>Ayuno</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -5401,12 +5405,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Tessa</t>
+          <t>Jax</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -5419,12 +5423,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Josiah</t>
+          <t>Tessa</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Oickle</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -5437,12 +5441,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Dion</t>
+          <t>Josiah</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Krause</t>
+          <t>Oickle</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -5455,12 +5459,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Vienne</t>
+          <t>Dion</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Wilkening</t>
+          <t>Krause</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -5473,12 +5477,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Jaykob</t>
+          <t>Vienne</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Oickle</t>
+          <t>Wilkening</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -5491,12 +5495,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Jaykob</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>VanLochem</t>
+          <t>Oickle</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -5509,12 +5513,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Blum</t>
+          <t>VanLochem</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -5527,12 +5531,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Gage</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Liebig</t>
+          <t>Blum</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -5545,12 +5549,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Gage</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>Liebig</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -5563,12 +5567,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -5581,12 +5585,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>AJ</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Celis</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -5599,12 +5603,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Adilynn</t>
+          <t>AJ</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Whiles</t>
+          <t>Celis</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -5617,12 +5621,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Adilynn</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Bovey</t>
+          <t>Whiles</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -5635,12 +5639,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Taya</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Ferguson</t>
+          <t>Bovey</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -5653,12 +5657,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Taya</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Glimsdale</t>
+          <t>Ferguson</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -5671,12 +5675,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Braiden</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Michnik</t>
+          <t>Glimsdale</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -5689,12 +5693,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Braiden</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>VanLochem</t>
+          <t>Michnik</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -5707,12 +5711,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Liliam</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Marinero</t>
+          <t>VanLochem</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -5725,12 +5729,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Richelle</t>
+          <t>Liliam</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Hansen</t>
+          <t>Marinero</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
@@ -5743,12 +5747,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Richelle</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Judd</t>
+          <t>Hansen</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -5761,12 +5765,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Seth</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Gill</t>
+          <t>Judd</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -5779,12 +5783,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Seth</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Bousquet</t>
+          <t>Gill</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -5797,12 +5801,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Bousquet</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -5815,12 +5819,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Michnik</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -5833,12 +5837,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Vickery</t>
+          <t>Michnik</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -5851,12 +5855,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Kolton</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Balaneski</t>
+          <t>Vickery</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
@@ -5869,12 +5873,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Sophia</t>
+          <t>Kolton</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Judd</t>
+          <t>Balaneski</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -5887,12 +5891,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>MacKenzie</t>
+          <t>Sophia</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Judd</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -5905,12 +5909,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Brooks</t>
+          <t>MacKenzie</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Hansen</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -5923,12 +5927,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>Brooks</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Webber</t>
+          <t>Hansen</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
@@ -5941,12 +5945,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Karston</t>
+          <t>Connor</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Loehndorf</t>
+          <t>Webber</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
@@ -5959,12 +5963,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Criszel</t>
+          <t>Karston</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Maraon</t>
+          <t>Loehndorf</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -5977,12 +5981,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Franko</t>
+          <t>Criszel</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Canton</t>
+          <t>Maraon</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -5995,12 +5999,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Franko</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Michnik</t>
+          <t>Canton</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -6013,12 +6017,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Michnik</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -6031,12 +6035,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Burke</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -6049,12 +6053,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Burke</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Liebig</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -6067,12 +6071,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Ivy</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Bovey</t>
+          <t>Liebig</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
@@ -6085,12 +6089,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Ivy</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Dore</t>
+          <t>Bovey</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
@@ -6103,12 +6107,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Bowen</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Dore</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
@@ -6121,12 +6125,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Steven</t>
+          <t>Bowen</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Ruppert</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
@@ -6139,12 +6143,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Coen</t>
+          <t>Steven</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Hansen</t>
+          <t>Ruppert</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
@@ -6157,12 +6161,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Coen</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Bakker</t>
+          <t>Hansen</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
@@ -6175,12 +6179,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Katelin</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Friesen</t>
+          <t>Bakker</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
@@ -6193,12 +6197,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Devin</t>
+          <t>Katelin</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Holzer</t>
+          <t>Friesen</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
@@ -6211,19 +6215,15 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Karissa</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>shawnmain@me.com</t>
-        </is>
-      </c>
+          <t>Holzer</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6233,15 +6233,19 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Dean</t>
+          <t>Karissa</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Lunde</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr"/>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>shawnmain@me.com</t>
+        </is>
+      </c>
       <c r="D298" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6251,19 +6255,15 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Brenda</t>
+          <t>Dean</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Wyntjes</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>pipercreekpetresort@outlook.com</t>
-        </is>
-      </c>
+          <t>Lunde</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6273,15 +6273,19 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Brady</t>
+          <t>Brenda</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Maaskant</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr"/>
+          <t>Wyntjes</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>pipercreekpetresort@outlook.com</t>
+        </is>
+      </c>
       <c r="D300" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6291,12 +6295,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Christ</t>
+          <t>Brady</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Keumoe</t>
+          <t>Maaskant</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
@@ -6309,12 +6313,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Pedro</t>
+          <t>Christ</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Bazzan</t>
+          <t>Keumoe</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
@@ -6327,12 +6331,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Linden</t>
+          <t>Pedro</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Skrodolis</t>
+          <t>Bazzan</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
@@ -6345,12 +6349,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Zylah</t>
+          <t>Linden</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Bizimana</t>
+          <t>Skrodolis</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
@@ -6363,19 +6367,15 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Danielle</t>
+          <t>Zylah</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Haessel</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>danielleparker482@hotmail.com</t>
-        </is>
-      </c>
+          <t>Bizimana</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6385,15 +6385,19 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>Danielle</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Skrodolis</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr"/>
+          <t>Haessel</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>danielleparker482@hotmail.com</t>
+        </is>
+      </c>
       <c r="D306" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6403,19 +6407,15 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Craig</t>
+          <t>Connor</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Gomez</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>craig.shawn.gomez@gmail.com</t>
-        </is>
-      </c>
+          <t>Skrodolis</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6425,17 +6425,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Craig</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Gizikoff</t>
+          <t>Gomez</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>info@lepagephc.ca</t>
+          <t>craig.shawn.gomez@gmail.com</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -6447,17 +6447,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Jeanne</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Botha</t>
+          <t>Gizikoff</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>righsbotha@gmail.com</t>
+          <t>info@lepagephc.ca</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -6469,7 +6469,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Deon</t>
+          <t>Jeanne</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>jidh300@gmail.com</t>
+          <t>righsbotha@gmail.com</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -6491,15 +6491,19 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Ellie</t>
+          <t>Deon</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Glover</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr"/>
+          <t>Botha</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>jidh300@gmail.com</t>
+        </is>
+      </c>
       <c r="D311" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6509,7 +6513,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Wendy</t>
+          <t>Ellie</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -6527,7 +6531,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Wendy</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -6545,19 +6549,15 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Shakil</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Papel</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>sk17papel@gmail.com</t>
-        </is>
-      </c>
+          <t>Glover</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6567,15 +6567,19 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Alyssa</t>
+          <t>Shakil</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Sherwin</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr"/>
+          <t>Papel</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>sk17papel@gmail.com</t>
+        </is>
+      </c>
       <c r="D315" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6585,12 +6589,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Seth</t>
+          <t>Alyssa</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Gill</t>
+          <t>Sherwin</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
@@ -6603,12 +6607,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Jai-Li</t>
+          <t>Seth</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Harvey</t>
+          <t>Gill</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
@@ -6621,12 +6625,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Raine</t>
+          <t>Jai-Li</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Joson</t>
+          <t>Harvey</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
@@ -6639,12 +6643,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Isaac</t>
+          <t>Raine</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Park</t>
+          <t>Joson</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
@@ -6657,12 +6661,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Fisher</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Dunphy</t>
+          <t>Park</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
@@ -6675,12 +6679,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Ayden</t>
+          <t>Fisher</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Quinlan</t>
+          <t>Dunphy</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
@@ -6693,12 +6697,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>Ayden</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>Quinlan</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
@@ -6711,12 +6715,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Marah</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Dunphy</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
@@ -6729,12 +6733,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Marah</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Fleck</t>
+          <t>Dunphy</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
@@ -6747,12 +6751,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>McRae</t>
+          <t>Fleck</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
@@ -6765,19 +6769,15 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Hanna</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Safron</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>hannasafron@icloud.com</t>
-        </is>
-      </c>
+          <t>McRae</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6787,15 +6787,19 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Hanna</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Howard</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr"/>
+          <t>Safron</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>hannasafron@icloud.com</t>
+        </is>
+      </c>
       <c r="D327" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6805,19 +6809,15 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Mila</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Haynes</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>cristinabagundol@yahoo.com</t>
-        </is>
-      </c>
+          <t>Howard</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6827,15 +6827,19 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Mila</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Robberstad</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr"/>
+          <t>Haynes</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>cristinabagundol@yahoo.com</t>
+        </is>
+      </c>
       <c r="D329" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6845,12 +6849,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Shayne</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Malsbury</t>
+          <t>Robberstad</t>
         </is>
       </c>
       <c r="C330" t="inlineStr"/>
@@ -6863,19 +6867,15 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>laura</t>
+          <t>Shayne</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>edwards</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>alfedwards58@gmail.com</t>
-        </is>
-      </c>
+          <t>Malsbury</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6885,15 +6885,19 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>laura</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>McClelland</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr"/>
+          <t>edwards</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>alfedwards58@gmail.com</t>
+        </is>
+      </c>
       <c r="D332" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6903,12 +6907,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Larry</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Vetter</t>
+          <t>McClelland</t>
         </is>
       </c>
       <c r="C333" t="inlineStr"/>
@@ -6921,7 +6925,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Larry</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -6939,12 +6943,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Fuchs</t>
+          <t>Vetter</t>
         </is>
       </c>
       <c r="C335" t="inlineStr"/>
@@ -6957,7 +6961,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Meyer</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -6975,19 +6979,15 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Serenna</t>
+          <t>Meyer</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Constable</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>reddeer@bredin.ca</t>
-        </is>
-      </c>
+          <t>Fuchs</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -6997,17 +6997,17 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Carter</t>
+          <t>Serenna</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Proft</t>
+          <t>Constable</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>carter.proft@iaprivatewealth.ca</t>
+          <t>reddeer@bredin.ca</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -7019,17 +7019,17 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Sakthi</t>
+          <t>Carter</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Aenugula</t>
+          <t>Proft</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>sakthiprasanth.aenugula@novachem.com</t>
+          <t>carter.proft@iaprivatewealth.ca</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -7041,15 +7041,19 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Nikki</t>
+          <t>Sakthi</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Januszewski</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr"/>
+          <t>Aenugula</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>sakthiprasanth.aenugula@novachem.com</t>
+        </is>
+      </c>
       <c r="D340" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7059,12 +7063,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Buffy</t>
+          <t>Nikki</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Robblee</t>
+          <t>Januszewski</t>
         </is>
       </c>
       <c r="C341" t="inlineStr"/>
@@ -7077,12 +7081,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Zoey</t>
+          <t>Buffy</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Januszewski</t>
+          <t>Robblee</t>
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
@@ -7095,12 +7099,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Zoey</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>McPeek</t>
+          <t>Januszewski</t>
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
@@ -7113,12 +7117,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Ella</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Januszewski</t>
+          <t>McPeek</t>
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
@@ -7131,12 +7135,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Barb</t>
+          <t>Ella</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Pfannmueler</t>
+          <t>Januszewski</t>
         </is>
       </c>
       <c r="C345" t="inlineStr"/>
@@ -7149,12 +7153,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Adyson</t>
+          <t>Barb</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Trepanier</t>
+          <t>Pfannmueler</t>
         </is>
       </c>
       <c r="C346" t="inlineStr"/>
@@ -7167,7 +7171,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Adyson</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -7185,7 +7189,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -7203,19 +7207,15 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Megan &amp; John</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Heinen</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>maheinen84@gmail.com</t>
-        </is>
-      </c>
+          <t>Trepanier</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7225,15 +7225,19 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Megan &amp; John</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Cote</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr"/>
+          <t>Heinen</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>maheinen84@gmail.com</t>
+        </is>
+      </c>
       <c r="D350" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7243,12 +7247,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Jayda</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Differenz</t>
+          <t>Cote</t>
         </is>
       </c>
       <c r="C351" t="inlineStr"/>
@@ -7261,19 +7265,15 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>julien</t>
+          <t>Jayda</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>kelly</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>kellyseamus=+1@hotmail.com</t>
-        </is>
-      </c>
+          <t>Differenz</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7283,17 +7283,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>julien</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Davison</t>
+          <t>kelly</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>jldav78@gmail.com</t>
+          <t>kellyseamus=+1@hotmail.com</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -7305,17 +7305,17 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Kaitlin</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Meier</t>
+          <t>Davison</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>kmeier@pivotalcpa.ca</t>
+          <t>jldav78@gmail.com</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -7327,17 +7327,17 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Tristin</t>
+          <t>Kaitlin</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Brisbois</t>
+          <t>Meier</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>tristin.brisbois@reddeer.ca</t>
+          <t>kmeier@pivotalcpa.ca</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -7349,17 +7349,17 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>leslie</t>
+          <t>Tristin</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>wright</t>
+          <t>Brisbois</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>leslie0985@hotmail.com</t>
+          <t>tristin.brisbois@reddeer.ca</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -7371,15 +7371,19 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>leslie</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr"/>
+          <t>wright</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>leslie0985@hotmail.com</t>
+        </is>
+      </c>
       <c r="D357" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7389,12 +7393,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Seija</t>
+          <t>Hunter</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Worth</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="C358" t="inlineStr"/>
@@ -7407,7 +7411,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Elias</t>
+          <t>Seija</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -7425,19 +7429,15 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Khryzzia Kaye</t>
+          <t>Elias</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Mendio</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>mendio.kaye@gmail.com</t>
-        </is>
-      </c>
+          <t>Worth</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7447,15 +7447,19 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Cohen</t>
+          <t>Khryzzia Kaye</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr"/>
+          <t>Mendio</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>mendio.kaye@gmail.com</t>
+        </is>
+      </c>
       <c r="D361" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7465,19 +7469,15 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Cohen</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Snider</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>jason@rdlawyers.ca</t>
-        </is>
-      </c>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7487,15 +7487,19 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Quinn</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Schmaltz</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr"/>
+          <t>Snider</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>jason@rdlawyers.ca</t>
+        </is>
+      </c>
       <c r="D363" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7505,12 +7509,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Quinn</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Kilbreath</t>
+          <t>Schmaltz</t>
         </is>
       </c>
       <c r="C364" t="inlineStr"/>
@@ -7523,7 +7527,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Jovi</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -7541,7 +7545,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Jovi</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -7559,7 +7563,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Rio</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -7577,19 +7581,15 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Christal</t>
+          <t>Rio</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Coupland</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>christalmargaret@gmail.com</t>
-        </is>
-      </c>
+          <t>Kilbreath</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7599,17 +7599,17 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Candace</t>
+          <t>Christal</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Misyk</t>
+          <t>Coupland</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>cmisyk@gmail.com</t>
+          <t>christalmargaret@gmail.com</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -7621,17 +7621,17 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>jack</t>
+          <t>Candace</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>misyk</t>
+          <t>Misyk</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>cmisyk+1@gmail.com</t>
+          <t>cmisyk@gmail.com</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -7643,17 +7643,17 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Brenda</t>
+          <t>jack</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Tams</t>
+          <t>misyk</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>tamsbrenda@gamil.com</t>
+          <t>cmisyk+1@gmail.com</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -7665,7 +7665,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Rick</t>
+          <t>Brenda</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>tamsfarm@xplornet.ca</t>
+          <t>tamsbrenda@gamil.com</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -7687,17 +7687,17 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Rommel</t>
+          <t>Rick</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Buriel</t>
+          <t>Tams</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>romjoy.rainbow@gmail.com</t>
+          <t>tamsfarm@xplornet.ca</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -7709,17 +7709,17 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Calvin</t>
+          <t>Rommel</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Maranga</t>
+          <t>Buriel</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>calvinmaranga16@gmail.com</t>
+          <t>romjoy.rainbow@gmail.com</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -7731,17 +7731,17 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Calvin</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Spicer</t>
+          <t>Maranga</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>albrea1971@gmail.com</t>
+          <t>calvinmaranga16@gmail.com</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -7753,17 +7753,17 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Denise</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Maranga</t>
+          <t>Spicer</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>denden.mushii@yahoo.com</t>
+          <t>albrea1971@gmail.com</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -7775,17 +7775,17 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Heather</t>
+          <t>Denise</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Griffiths</t>
+          <t>Maranga</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>heather_mclaren@hotmail.com</t>
+          <t>denden.mushii@yahoo.com</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -7797,17 +7797,17 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Judy</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Toor</t>
+          <t>Griffiths</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>judy.toor@gmail.com</t>
+          <t>heather_mclaren@hotmail.com</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -7819,17 +7819,17 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>clarissa</t>
+          <t>Judy</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>maranga</t>
+          <t>Toor</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>clarissa_maranga@yahoo.com</t>
+          <t>judy.toor@gmail.com</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -7841,17 +7841,17 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Doug</t>
+          <t>clarissa</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Maranga</t>
+          <t>maranga</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>doug.maranga@yahoo.com</t>
+          <t>clarissa_maranga@yahoo.com</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -7863,15 +7863,19 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Harper</t>
+          <t>Doug</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Griffiths</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr"/>
+          <t>Maranga</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>doug.maranga@yahoo.com</t>
+        </is>
+      </c>
       <c r="D381" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7881,19 +7885,15 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Harper</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Ho</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>sammy.shogun@gmail.com</t>
-        </is>
-      </c>
+          <t>Griffiths</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -7903,17 +7903,17 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Jerry</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Espino</t>
+          <t>Ho</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>jerryespino@hotmail.com</t>
+          <t>sammy.shogun@gmail.com</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -7925,17 +7925,17 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Rodney</t>
+          <t>Jerry</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Lim</t>
+          <t>Espino</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>rodneylim46@gmail.com</t>
+          <t>jerryespino@hotmail.com</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -7947,17 +7947,17 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Dev</t>
+          <t>Rodney</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Aggarwal</t>
+          <t>Lim</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>westparkida@gmail.com</t>
+          <t>rodneylim46@gmail.com</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -7969,17 +7969,17 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>greg</t>
+          <t>Dev</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>pollan</t>
+          <t>Aggarwal</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>gregpollon65@outlook.com</t>
+          <t>westparkida@gmail.com</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -7991,17 +7991,17 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Kenneth</t>
+          <t>greg</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Tong</t>
+          <t>pollan</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>tongk88@gmail.com</t>
+          <t>gregpollon65@outlook.com</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -8013,17 +8013,17 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Marianne</t>
+          <t>Kenneth</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Badenhorst</t>
+          <t>Tong</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>mariannebadenhorst@gmail.com</t>
+          <t>tongk88@gmail.com</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -8035,17 +8035,17 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Dale</t>
+          <t>Marianne</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Joyal</t>
+          <t>Badenhorst</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>daleajoyal1963@gmasil.com</t>
+          <t>mariannebadenhorst@gmail.com</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -8057,17 +8057,17 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Terry</t>
+          <t>Dale</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Tonsi</t>
+          <t>Joyal</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>ttonsi@hotmail.com</t>
+          <t>daleajoyal1963@gmasil.com</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -8079,17 +8079,17 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Gail</t>
+          <t>Terry</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Sanders</t>
+          <t>Tonsi</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>sesrungail@gmail.com</t>
+          <t>ttonsi@hotmail.com</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -8101,17 +8101,17 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Sheila</t>
+          <t>Gail</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Crouch</t>
+          <t>Sanders</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>sheila+@pickleplex.ca</t>
+          <t>sesrungail@gmail.com</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -8123,17 +8123,17 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Bob</t>
+          <t>Sheila</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Sanders</t>
+          <t>Crouch</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>rgswildcat1@outlook.com</t>
+          <t>sheila+@pickleplex.ca</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -8145,17 +8145,17 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Candace</t>
+          <t>Bob</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Tonsi</t>
+          <t>Sanders</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>ctonsi@hotmail.ca</t>
+          <t>rgswildcat1@outlook.com</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -8167,17 +8167,17 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Candace</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Darling</t>
+          <t>Tonsi</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>jd@mapletree.ca</t>
+          <t>ctonsi@hotmail.ca</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -8189,17 +8189,17 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Andreas</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Kusuma</t>
+          <t>Darling</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>macogpk@hotmail.com</t>
+          <t>jd@mapletree.ca</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -8211,17 +8211,17 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Volunteer</t>
+          <t>Andreas</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>RDPC</t>
+          <t>Kusuma</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>club+@reddeerpickleball.com</t>
+          <t>macogpk@hotmail.com</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -8233,17 +8233,17 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Wade</t>
+          <t>Volunteer</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Schafer</t>
+          <t>RDPC</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>wschafer08@gmail.com</t>
+          <t>club+@reddeerpickleball.com</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -8255,17 +8255,17 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Wade</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>Schafer</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>jonnnybell@gmail.com</t>
+          <t>wschafer08@gmail.com</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -8277,17 +8277,17 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Carly</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Farion</t>
+          <t>Bell</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>carlyfarion@telus.net</t>
+          <t>jonnnybell@gmail.com</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -8299,17 +8299,17 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>RDPC</t>
+          <t>Carly</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Tournament</t>
+          <t>Farion</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>treasurer@reddeerpickleball.com</t>
+          <t>carlyfarion@telus.net</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -8321,17 +8321,17 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>RDPC</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Tournament</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>esmith01@live.ca</t>
+          <t>treasurer@reddeerpickleball.com</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -8343,17 +8343,17 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Carruthers</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>sammulake@hotmail.com</t>
+          <t>esmith01@live.ca</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -8365,17 +8365,17 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Hollett</t>
+          <t>Carruthers</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>gdhollet@icloud.com</t>
+          <t>sammulake@hotmail.com</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -8387,17 +8387,17 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Presley</t>
+          <t>Hollett</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>sarahpresley36@gmail.com</t>
+          <t>gdhollet@icloud.com</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -8409,17 +8409,17 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Judy</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Toor</t>
+          <t>Presley</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>m-poor@shaw.ca</t>
+          <t>sarahpresley36@gmail.com</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -8431,17 +8431,17 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Elina</t>
+          <t>Judy</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Upward</t>
+          <t>Toor</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>elinabelle2014@gmail.com</t>
+          <t>m-poor@shaw.ca</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -8453,17 +8453,17 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Elina</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Carter</t>
+          <t>Upward</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>jessica.e.arterone@gmail.com</t>
+          <t>elinabelle2014@gmail.com</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -8475,17 +8475,17 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Ken</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Elver</t>
+          <t>Carter</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>ken.alver@gmail.com</t>
+          <t>jessica.e.arterone@gmail.com</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -8497,17 +8497,17 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Ken</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Schellenberg</t>
+          <t>Elver</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>hischellenberg@gmail.com</t>
+          <t>ken.alver@gmail.com</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -8519,17 +8519,17 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Reid</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Prystai</t>
+          <t>Schellenberg</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>reid.prystai@gmail.com</t>
+          <t>hischellenberg@gmail.com</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -8541,17 +8541,17 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Reid</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Walsh</t>
+          <t>Prystai</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>matt.walsh@gmail.com</t>
+          <t>reid.prystai@gmail.com</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -8563,17 +8563,17 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Richard</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>PATTERSON</t>
+          <t>Walsh</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>rjpatterson101@googlemail.com</t>
+          <t>matt.walsh@gmail.com</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -8585,17 +8585,17 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Hreat</t>
+          <t>Richard</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Bnabsa</t>
+          <t>PATTERSON</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>hreatbba24@gmail.com</t>
+          <t>rjpatterson101@googlemail.com</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -8607,17 +8607,17 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Suzanne</t>
+          <t>Hreat</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Aylward</t>
+          <t>Bnabsa</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>suzanneaylward@yahoo.ca</t>
+          <t>hreatbba24@gmail.com</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -8629,15 +8629,19 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Suzanne</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Schellenberg</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr"/>
+          <t>Aylward</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>suzanneaylward@yahoo.ca</t>
+        </is>
+      </c>
       <c r="D416" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -8647,19 +8651,15 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Armstrong</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>carriearmstrong+1@live.com</t>
-        </is>
-      </c>
+          <t>Schellenberg</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
@@ -8669,17 +8669,17 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Keith</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Spady</t>
+          <t>Armstrong</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>spadybk@shaw.ca</t>
+          <t>carriearmstrong+1@live.com</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -8691,17 +8691,17 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Charolette</t>
+          <t>Keith</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Doffett</t>
+          <t>Spady</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>charolette.doffett@gmail.com</t>
+          <t>spadybk@shaw.ca</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -8713,17 +8713,17 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Charolette</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Walters</t>
+          <t>Doffett</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>nancyjoy@telus.net</t>
+          <t>charolette.doffett@gmail.com</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -8735,17 +8735,17 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Chandler</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Duffett</t>
+          <t>Walters</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>chandler.duffett@gmail.com</t>
+          <t>nancyjoy@telus.net</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -8757,17 +8757,17 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Amanda</t>
+          <t>Chandler</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Duffett</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>amanda.wilson@rdpsd.ab.ca</t>
+          <t>chandler.duffett@gmail.com</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -8779,17 +8779,17 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Patrica</t>
+          <t>Amanda</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Viado</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>patricaviado@gmail.com</t>
+          <t>amanda.wilson@rdpsd.ab.ca</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -8801,17 +8801,17 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Patrica</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Prystai</t>
+          <t>Viado</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>michelle.yunnch@gmail.com</t>
+          <t>patricaviado@gmail.com</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -8823,17 +8823,17 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Horembala</t>
+          <t>Prystai</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>paddling@telus.net</t>
+          <t>michelle.yunnch@gmail.com</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -8845,20 +8845,922 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Horembala</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>paddling@telus.net</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
           <t>Carrie</t>
         </is>
       </c>
-      <c r="B426" t="inlineStr">
+      <c r="B427" t="inlineStr">
         <is>
           <t>Armstrong</t>
         </is>
       </c>
-      <c r="C426" t="inlineStr">
+      <c r="C427" t="inlineStr">
         <is>
           <t>carriearmstrong@live.com</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr">
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Bonny</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Bickley</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>bybickley@gmail.com</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Watson</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>andyianwatson@gmail.com</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Siera</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Mctaggart</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>siera.michalsky@gmail.com</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Rosmary</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Gilmore</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>rosmary.gilmore@btinternet.com</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Watson</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>sarawatson5131@gmail.com</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Leonard</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Mctaggart</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>lmcteggart@live.ca</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Patterson</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>akepatterson@googlemail.com</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Sheridan</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Hendricks</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>sheridanhendricks@live.com</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Logan</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Walkey</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>sh_k@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Viterbo</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>gladysmay.oro@gmail.com</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Caitlin</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Andrews</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>caitlin.andrews@elitechiropractic.ca</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Debb</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Dickie</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>j-dickie@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Graeme</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Paine</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>gpaine93@gmail.com</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Oscar</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Graham</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>oscarjg2001@icloud.com</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Phelps</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>draytonjen9@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Glenn</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Dickie</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>g-ddickie@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Egdon</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Gonzales</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>egdonmark@gmail.com</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Chantel</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Gafour</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>chantelgafour@gmail.com</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Arg</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Gafour</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>gafour99@gmail.com</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Evangelista</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>camille_happyheart@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Clint</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>clintpereira@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Roger</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Blager</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>rogerblager@gmail.com</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Lois</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Hornung</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>lois.hornung@gmail.com</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Wayne</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Anderson</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>patwayand622@gmail.com</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>byron</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>lee</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>byronlee@live.ca</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Jackie</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Tomalty</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>jackie.tomalty2020@gmail.com</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Tyler</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>McDonald</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>tymcdonald98@gmail.com</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Brian</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Worth</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>bworth@protonmail.com</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Cody</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Webber</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>codywebber8@gmail.com</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Jean</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Mendoza</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>jeancamillemendoza@proton.me</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Ella</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Parcels</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>ellaparcelss@gmail.com</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Kelvin</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>kelvinr.fernando@proton.me</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Daryn</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Hebert</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>daryn.hebert7@gmail.com</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Madison</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Walter</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>mgeopano8@gmail.com</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Toby</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Turnbull</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>tobyturnbull@ymail.com</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Pickleball Alberta</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Referee Clinic</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>doug.eyers55@gmail.com</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Braden</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Luke</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>tluke815+@hotamil.com</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Pathemae</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Dael</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>pathemae.dael@gmail.com</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Tyson</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Luke</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>tluke815@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>reddeer@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Dave</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Luke</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>daveluke@shaw.ca</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
         <is>
           <t>reddeer@pickleplex.ca</t>
         </is>
